--- a/docs/phase4/ALL_RESULTS.xlsx
+++ b/docs/phase4/ALL_RESULTS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faisa\Documents\GitHub\Metaphorical_Analysis\docs\phase4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89A24D43-C3FB-42AF-A54C-795720277C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FFDA722-27C1-4810-9D41-4E925CB34112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="14586" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="394">
   <si>
     <t>Experiment</t>
   </si>
@@ -306,6 +306,30 @@
     <t>1-of-3 = positive if ANY of the 3 chosen configs says true. Ranking by recall favors liberal configurations; the 1-of-3 OR typically trades precision for recall.</t>
   </si>
   <si>
+    <t>Fixed combo (user-requested, not recall-selected)</t>
+  </si>
+  <si>
+    <t>Gemini-FS + GPT-Z + Claude-FS (1-of-3) [A]</t>
+  </si>
+  <si>
+    <t>Fixed combo: positive if ANY of Gemini few-shot, GPT zero-shot, Claude few-shot says true -- not the recall-selected Top 3 above.</t>
+  </si>
+  <si>
+    <t>Gemini-FS + GPT-Z + Claude-FS (1-of-3) [B]</t>
+  </si>
+  <si>
+    <t>Gemini-FS + GPT-Z + Claude-FS (1-of-3) [C]</t>
+  </si>
+  <si>
+    <t>Gemini-FS + GPT-Z + Claude-FS (1-of-3) [D]</t>
+  </si>
+  <si>
+    <t>Gemini-FS + GPT-Z + Claude-FS (1-of-3) [D2]</t>
+  </si>
+  <si>
+    <t>Gemini-FS + GPT-Z + Claude-FS (1-of-3) MEAN over 5 sets</t>
+  </si>
+  <si>
     <t>GPT-Z + Claude-FS combination</t>
   </si>
   <si>
@@ -567,6 +591,33 @@
     <t>1-of-3 = positive if ANY of the 3 chosen configs says true.</t>
   </si>
   <si>
+    <t>Gemini-FS + GPT-Z + Claude-FS (1-of-3) [M1]</t>
+  </si>
+  <si>
+    <t>Gemini-FS + GPT-Z + Claude-FS (1-of-3) [M2]</t>
+  </si>
+  <si>
+    <t>Gemini-FS + GPT-Z + Claude-FS (1-of-3) [E1]</t>
+  </si>
+  <si>
+    <t>Gemini-FS + GPT-Z + Claude-FS (1-of-3) [E2]</t>
+  </si>
+  <si>
+    <t>Gemini-FS + GPT-Z + Claude-FS (1-of-3) [H1]</t>
+  </si>
+  <si>
+    <t>Gemini-FS + GPT-Z + Claude-FS (1-of-3) [H2]</t>
+  </si>
+  <si>
+    <t>Gemini-FS + GPT-Z + Claude-FS (1-of-3) [Q1]</t>
+  </si>
+  <si>
+    <t>Gemini-FS + GPT-Z + Claude-FS (1-of-3) [Q2]</t>
+  </si>
+  <si>
+    <t>Gemini-FS + GPT-Z + Claude-FS (1-of-3) MEAN over 8 sets</t>
+  </si>
+  <si>
     <t>GPT-Z OR Claude-FS [M1]</t>
   </si>
   <si>
@@ -681,6 +732,12 @@
     <t>Zero-shot (Z) was never run on the 50-poem multi-poet pool -- GPT-Z does not exist here.</t>
   </si>
   <si>
+    <t>Gemini-FS + GPT-Z + Claude-FS (1-of-3): N/A on this sheet</t>
+  </si>
+  <si>
+    <t>Same reason -- this fixed combo requires GPT-Z, which was never run on the 50-poem multi-poet pool.</t>
+  </si>
+  <si>
     <t>Ensemble (majority vote across Claude/GPT/Gemini), per set</t>
   </si>
   <si>
@@ -750,6 +807,9 @@
     <t>Chosen 3: Claude-A (R=0.819), GPT-Z (R=0.732), GPT-A (R=0.677).</t>
   </si>
   <si>
+    <t>Fixed combo: positive if ANY of Gemini few-shot[A], GPT zero-shot, Claude few-shot[A] says true -- not the recall-selected Top 3 above.</t>
+  </si>
+  <si>
     <t>GPT-Z + Claude-FS[A] combination</t>
   </si>
   <si>
@@ -831,6 +891,9 @@
     <t>Chosen 3: Gemini-FS (R=0.800), Claude-FS (R=0.600), Gemini-Z (R=0.533).</t>
   </si>
   <si>
+    <t>Gemini-FS + GPT-Z + Claude-FS (1-of-3)</t>
+  </si>
+  <si>
     <t>GPT-Z + Claude-FS combination (reused from analysis_report_phase7.json)</t>
   </si>
   <si>
@@ -1059,7 +1122,7 @@
     <t>0.406 (ENSEMBLE(2of3)/zero)</t>
   </si>
   <si>
-    <t>0.281 (GPT-Z OR Claude-FS)</t>
+    <t>0.271 (Gemini-FS+GPT-Z+Claude-FS(1of3))</t>
   </si>
   <si>
     <t>GPT-FS (R=0.800), GPT-Z (R=0.600), Claude-Z (R=0.520)</t>
@@ -1095,6 +1158,9 @@
     <t>GPT-Z OR Claude-FS / AND: the 2-voter combination of GPT-5.4-mini's zero-shot call with Claude Sonnet 4.6's few-shot call for the stated set. OR = positive if either says yes; AND = positive only if both agree. This is the project's own 'production candidate' combination, first analyzed in docs/phase4/DESIGN_CHOICE_GPTZ_CLAUDEFS.md.</t>
   </si>
   <si>
+    <t>Gemini-FS + GPT-Z + Claude-FS (1-of-3): a FIXED 3-voter combination requested directly by the user (Gemini few-shot, GPT zero-shot, Claude few-shot), scored as 1-of-3 (OR -- positive if ANY of the 3 says true). This is NOT the recall-selected 'Top 3' above -- it is always this exact trio, on every sheet where all 3 inputs exist. Shown per few-shot set + MEAN on 'E1v2 Core' and 'Eras FewShot' (same convention as every other combo row); a single row on 'Opus5.5 SetA' (set A only) and each Phase 7 subtype sheet (1 few-shot condition only); N/A on 'Multipoet F5F10' (no zero-shot run on that pool, so GPT-Z does not exist there) and on 'Phase1 Frozen' (different metric entirely).</t>
+  </si>
+  <si>
     <t>MEAN (over sets) rows: the MEAN of each set's own already-computed Precision/Recall/F1 (not derived from averaged TP/FP/FN, which would be a different, nonlinear quantity for F1). TP/FP/FN shown on a MEAN row are plain means of the per-set counts, shown for reference only (hence non-integer) -- they are NOT used to (re)derive that row's P/R/F1. The 'never pick the best set' rule means every individual set's row is always shown alongside the MEAN, with the full min-max range stated in that row's Notes cell.</t>
   </si>
   <si>
@@ -1158,7 +1224,7 @@
     <t>Provenance</t>
   </si>
   <si>
-    <t>Built by scripts/build_results_excel.py, git commit 251826c870569c05c9b2a2d8c075af176e180b4e, generated 2026-10-30 07:48 UTC. No API calls were made to produce this workbook or any of its inputs.</t>
+    <t>Built by scripts/build_results_excel.py, git commit 5828026ab8d850273497e9c42b9da47057d47c9b, generated 2026-10-30 08:08 UTC. No API calls were made to produce this workbook or any of its inputs.</t>
   </si>
 </sst>
 </file>
@@ -1596,7 +1662,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr defaultRowHeight="14.35"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -3248,378 +3314,584 @@
         <v>88</v>
       </c>
       <c r="B66" s="7">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C66" s="7">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D66" s="7">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E66" s="7">
-        <f t="shared" ref="E66:E77" si="8">327-B66-C66-D66</f>
-        <v>48</v>
+        <f t="shared" ref="E66:E71" si="8">327-B66-C66-D66</f>
+        <v>45</v>
       </c>
       <c r="F66" s="8">
         <f>IFERROR(B66/(B66+C66),0)</f>
-        <v>0.41984732824427479</v>
+        <v>0.42379182156133827</v>
       </c>
       <c r="G66" s="8">
         <f>IFERROR(B66/(B66+D66),0)</f>
-        <v>0.86614173228346458</v>
+        <v>0.89763779527559051</v>
       </c>
       <c r="H66" s="8">
         <f>IFERROR(2*F66*G66/(F66+G66),0)</f>
-        <v>0.56555269922879181</v>
-      </c>
-      <c r="I66" s="5"/>
+        <v>0.57575757575757569</v>
+      </c>
+      <c r="I66" s="5" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="67" spans="1:9">
       <c r="A67" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B67" s="5">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C67" s="5">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="D67" s="5">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E67" s="5">
         <f t="shared" si="8"/>
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F67" s="6">
         <f>IFERROR(B67/(B67+C67),0)</f>
-        <v>0.41960784313725491</v>
+        <v>0.41417910447761191</v>
       </c>
       <c r="G67" s="6">
         <f>IFERROR(B67/(B67+D67),0)</f>
-        <v>0.84251968503937003</v>
+        <v>0.87401574803149606</v>
       </c>
       <c r="H67" s="6">
         <f>IFERROR(2*F67*G67/(F67+G67),0)</f>
-        <v>0.56020942408376972</v>
+        <v>0.5620253164556962</v>
       </c>
       <c r="I67" s="5"/>
     </row>
     <row r="68" spans="1:9">
       <c r="A68" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B68" s="5">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C68" s="5">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="D68" s="5">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E68" s="5">
         <f t="shared" si="8"/>
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="F68" s="6">
         <f>IFERROR(B68/(B68+C68),0)</f>
-        <v>0.42920353982300885</v>
+        <v>0.43568464730290457</v>
       </c>
       <c r="G68" s="6">
         <f>IFERROR(B68/(B68+D68),0)</f>
-        <v>0.76377952755905509</v>
+        <v>0.82677165354330706</v>
       </c>
       <c r="H68" s="6">
         <f>IFERROR(2*F68*G68/(F68+G68),0)</f>
-        <v>0.54957507082152979</v>
+        <v>0.57065217391304346</v>
       </c>
       <c r="I68" s="5"/>
     </row>
     <row r="69" spans="1:9">
       <c r="A69" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B69" s="5">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C69" s="5">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D69" s="5">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E69" s="5">
         <f t="shared" si="8"/>
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F69" s="6">
         <f>IFERROR(B69/(B69+C69),0)</f>
-        <v>0.41767068273092367</v>
+        <v>0.421875</v>
       </c>
       <c r="G69" s="6">
         <f>IFERROR(B69/(B69+D69),0)</f>
-        <v>0.81889763779527558</v>
+        <v>0.85039370078740162</v>
       </c>
       <c r="H69" s="6">
         <f>IFERROR(2*F69*G69/(F69+G69),0)</f>
-        <v>0.55319148936170215</v>
+        <v>0.56396866840731075</v>
       </c>
       <c r="I69" s="5"/>
     </row>
     <row r="70" spans="1:9">
       <c r="A70" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B70" s="5">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C70" s="5">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="D70" s="5">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E70" s="5">
         <f t="shared" si="8"/>
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="F70" s="6">
         <f>IFERROR(B70/(B70+C70),0)</f>
-        <v>0.41832669322709165</v>
+        <v>0.4188679245283019</v>
       </c>
       <c r="G70" s="6">
         <f>IFERROR(B70/(B70+D70),0)</f>
-        <v>0.82677165354330706</v>
+        <v>0.87401574803149606</v>
       </c>
       <c r="H70" s="6">
         <f>IFERROR(2*F70*G70/(F70+G70),0)</f>
-        <v>0.55555555555555558</v>
+        <v>0.56632653061224503</v>
       </c>
       <c r="I70" s="5"/>
     </row>
     <row r="71" spans="1:9">
       <c r="A71" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B71" s="10">
         <f>AVERAGE(B66,B67,B68,B69,B70)</f>
-        <v>104.6</v>
+        <v>109.8</v>
       </c>
       <c r="C71" s="10">
         <f>AVERAGE(C66,C67,C68,C69,C70)</f>
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="D71" s="10">
         <f>AVERAGE(D66,D67,D68,D69,D70)</f>
-        <v>22.4</v>
+        <v>17.2</v>
       </c>
       <c r="E71" s="10">
         <f t="shared" si="8"/>
-        <v>56.000000000000007</v>
+        <v>49.999999999999986</v>
       </c>
       <c r="F71" s="11">
         <f>AVERAGE(F66,F67,F68,F69,F70)</f>
-        <v>0.42093121743251077</v>
+        <v>0.42287969957403132</v>
       </c>
       <c r="G71" s="11">
         <f>AVERAGE(G66,G67,G68,G69,G70)</f>
-        <v>0.82362204724409449</v>
+        <v>0.86456692913385835</v>
       </c>
       <c r="H71" s="11">
         <f>AVERAGE(H66,H67,H68,H69,H70)</f>
-        <v>0.55681684781026985</v>
-      </c>
-      <c r="I71" s="9"/>
+        <v>0.56774605302917425</v>
+      </c>
+      <c r="I71" s="9" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="72" spans="1:9">
-      <c r="A72" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="B72" s="5">
-        <v>87</v>
-      </c>
-      <c r="C72" s="5">
-        <v>97</v>
-      </c>
-      <c r="D72" s="5">
-        <v>40</v>
-      </c>
-      <c r="E72" s="5">
-        <f t="shared" si="8"/>
-        <v>103</v>
-      </c>
-      <c r="F72" s="6">
-        <f>IFERROR(B72/(B72+C72),0)</f>
-        <v>0.47282608695652173</v>
-      </c>
-      <c r="G72" s="6">
-        <f>IFERROR(B72/(B72+D72),0)</f>
-        <v>0.68503937007874016</v>
-      </c>
-      <c r="H72" s="6">
-        <f>IFERROR(2*F72*G72/(F72+G72),0)</f>
-        <v>0.55948553054662387</v>
-      </c>
-      <c r="I72" s="5"/>
+      <c r="A72" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
     </row>
     <row r="73" spans="1:9">
-      <c r="A73" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B73" s="5">
-        <v>80</v>
-      </c>
-      <c r="C73" s="5">
-        <v>94</v>
-      </c>
-      <c r="D73" s="5">
-        <v>47</v>
-      </c>
-      <c r="E73" s="5">
-        <f t="shared" si="8"/>
-        <v>106</v>
-      </c>
-      <c r="F73" s="6">
+      <c r="A73" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B73" s="7">
+        <v>110</v>
+      </c>
+      <c r="C73" s="7">
+        <v>152</v>
+      </c>
+      <c r="D73" s="7">
+        <v>17</v>
+      </c>
+      <c r="E73" s="7">
+        <f t="shared" ref="E73:E84" si="9">327-B73-C73-D73</f>
+        <v>48</v>
+      </c>
+      <c r="F73" s="8">
         <f>IFERROR(B73/(B73+C73),0)</f>
-        <v>0.45977011494252873</v>
-      </c>
-      <c r="G73" s="6">
+        <v>0.41984732824427479</v>
+      </c>
+      <c r="G73" s="8">
         <f>IFERROR(B73/(B73+D73),0)</f>
-        <v>0.62992125984251968</v>
-      </c>
-      <c r="H73" s="6">
+        <v>0.86614173228346458</v>
+      </c>
+      <c r="H73" s="8">
         <f>IFERROR(2*F73*G73/(F73+G73),0)</f>
-        <v>0.53156146179401986</v>
+        <v>0.56555269922879181</v>
       </c>
       <c r="I73" s="5"/>
     </row>
     <row r="74" spans="1:9">
       <c r="A74" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B74" s="5">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="C74" s="5">
-        <v>46</v>
+        <v>148</v>
       </c>
       <c r="D74" s="5">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="E74" s="5">
-        <f t="shared" si="8"/>
-        <v>154</v>
+        <f t="shared" si="9"/>
+        <v>52</v>
       </c>
       <c r="F74" s="6">
         <f>IFERROR(B74/(B74+C74),0)</f>
-        <v>0.48888888888888887</v>
+        <v>0.41960784313725491</v>
       </c>
       <c r="G74" s="6">
         <f>IFERROR(B74/(B74+D74),0)</f>
-        <v>0.34645669291338582</v>
+        <v>0.84251968503937003</v>
       </c>
       <c r="H74" s="6">
         <f>IFERROR(2*F74*G74/(F74+G74),0)</f>
-        <v>0.40552995391705066</v>
+        <v>0.56020942408376972</v>
       </c>
       <c r="I74" s="5"/>
     </row>
     <row r="75" spans="1:9">
       <c r="A75" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B75" s="5">
         <v>97</v>
       </c>
-      <c r="B75" s="5">
-        <v>82</v>
-      </c>
       <c r="C75" s="5">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="D75" s="5">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E75" s="5">
-        <f t="shared" si="8"/>
-        <v>115</v>
+        <f t="shared" si="9"/>
+        <v>71</v>
       </c>
       <c r="F75" s="6">
         <f>IFERROR(B75/(B75+C75),0)</f>
-        <v>0.49101796407185627</v>
+        <v>0.42920353982300885</v>
       </c>
       <c r="G75" s="6">
         <f>IFERROR(B75/(B75+D75),0)</f>
-        <v>0.64566929133858264</v>
+        <v>0.76377952755905509</v>
       </c>
       <c r="H75" s="6">
         <f>IFERROR(2*F75*G75/(F75+G75),0)</f>
+        <v>0.54957507082152979</v>
+      </c>
+      <c r="I75" s="5"/>
+    </row>
+    <row r="76" spans="1:9">
+      <c r="A76" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B76" s="5">
+        <v>104</v>
+      </c>
+      <c r="C76" s="5">
+        <v>145</v>
+      </c>
+      <c r="D76" s="5">
+        <v>23</v>
+      </c>
+      <c r="E76" s="5">
+        <f t="shared" si="9"/>
+        <v>55</v>
+      </c>
+      <c r="F76" s="6">
+        <f>IFERROR(B76/(B76+C76),0)</f>
+        <v>0.41767068273092367</v>
+      </c>
+      <c r="G76" s="6">
+        <f>IFERROR(B76/(B76+D76),0)</f>
+        <v>0.81889763779527558</v>
+      </c>
+      <c r="H76" s="6">
+        <f>IFERROR(2*F76*G76/(F76+G76),0)</f>
+        <v>0.55319148936170215</v>
+      </c>
+      <c r="I76" s="5"/>
+    </row>
+    <row r="77" spans="1:9">
+      <c r="A77" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B77" s="5">
+        <v>105</v>
+      </c>
+      <c r="C77" s="5">
+        <v>146</v>
+      </c>
+      <c r="D77" s="5">
+        <v>22</v>
+      </c>
+      <c r="E77" s="5">
+        <f t="shared" si="9"/>
+        <v>54</v>
+      </c>
+      <c r="F77" s="6">
+        <f>IFERROR(B77/(B77+C77),0)</f>
+        <v>0.41832669322709165</v>
+      </c>
+      <c r="G77" s="6">
+        <f>IFERROR(B77/(B77+D77),0)</f>
+        <v>0.82677165354330706</v>
+      </c>
+      <c r="H77" s="6">
+        <f>IFERROR(2*F77*G77/(F77+G77),0)</f>
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="I77" s="5"/>
+    </row>
+    <row r="78" spans="1:9">
+      <c r="A78" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="B78" s="10">
+        <f>AVERAGE(B73,B74,B75,B76,B77)</f>
+        <v>104.6</v>
+      </c>
+      <c r="C78" s="10">
+        <f>AVERAGE(C73,C74,C75,C76,C77)</f>
+        <v>144</v>
+      </c>
+      <c r="D78" s="10">
+        <f>AVERAGE(D73,D74,D75,D76,D77)</f>
+        <v>22.4</v>
+      </c>
+      <c r="E78" s="10">
+        <f t="shared" si="9"/>
+        <v>56.000000000000007</v>
+      </c>
+      <c r="F78" s="11">
+        <f>AVERAGE(F73,F74,F75,F76,F77)</f>
+        <v>0.42093121743251077</v>
+      </c>
+      <c r="G78" s="11">
+        <f>AVERAGE(G73,G74,G75,G76,G77)</f>
+        <v>0.82362204724409449</v>
+      </c>
+      <c r="H78" s="11">
+        <f>AVERAGE(H73,H74,H75,H76,H77)</f>
+        <v>0.55681684781026985</v>
+      </c>
+      <c r="I78" s="9"/>
+    </row>
+    <row r="79" spans="1:9">
+      <c r="A79" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B79" s="5">
+        <v>87</v>
+      </c>
+      <c r="C79" s="5">
+        <v>97</v>
+      </c>
+      <c r="D79" s="5">
+        <v>40</v>
+      </c>
+      <c r="E79" s="5">
+        <f t="shared" si="9"/>
+        <v>103</v>
+      </c>
+      <c r="F79" s="6">
+        <f>IFERROR(B79/(B79+C79),0)</f>
+        <v>0.47282608695652173</v>
+      </c>
+      <c r="G79" s="6">
+        <f>IFERROR(B79/(B79+D79),0)</f>
+        <v>0.68503937007874016</v>
+      </c>
+      <c r="H79" s="6">
+        <f>IFERROR(2*F79*G79/(F79+G79),0)</f>
+        <v>0.55948553054662387</v>
+      </c>
+      <c r="I79" s="5"/>
+    </row>
+    <row r="80" spans="1:9">
+      <c r="A80" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B80" s="5">
+        <v>80</v>
+      </c>
+      <c r="C80" s="5">
+        <v>94</v>
+      </c>
+      <c r="D80" s="5">
+        <v>47</v>
+      </c>
+      <c r="E80" s="5">
+        <f t="shared" si="9"/>
+        <v>106</v>
+      </c>
+      <c r="F80" s="6">
+        <f>IFERROR(B80/(B80+C80),0)</f>
+        <v>0.45977011494252873</v>
+      </c>
+      <c r="G80" s="6">
+        <f>IFERROR(B80/(B80+D80),0)</f>
+        <v>0.62992125984251968</v>
+      </c>
+      <c r="H80" s="6">
+        <f>IFERROR(2*F80*G80/(F80+G80),0)</f>
+        <v>0.53156146179401986</v>
+      </c>
+      <c r="I80" s="5"/>
+    </row>
+    <row r="81" spans="1:9">
+      <c r="A81" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B81" s="5">
+        <v>44</v>
+      </c>
+      <c r="C81" s="5">
+        <v>46</v>
+      </c>
+      <c r="D81" s="5">
+        <v>83</v>
+      </c>
+      <c r="E81" s="5">
+        <f t="shared" si="9"/>
+        <v>154</v>
+      </c>
+      <c r="F81" s="6">
+        <f>IFERROR(B81/(B81+C81),0)</f>
+        <v>0.48888888888888887</v>
+      </c>
+      <c r="G81" s="6">
+        <f>IFERROR(B81/(B81+D81),0)</f>
+        <v>0.34645669291338582</v>
+      </c>
+      <c r="H81" s="6">
+        <f>IFERROR(2*F81*G81/(F81+G81),0)</f>
+        <v>0.40552995391705066</v>
+      </c>
+      <c r="I81" s="5"/>
+    </row>
+    <row r="82" spans="1:9">
+      <c r="A82" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B82" s="5">
+        <v>82</v>
+      </c>
+      <c r="C82" s="5">
+        <v>85</v>
+      </c>
+      <c r="D82" s="5">
+        <v>45</v>
+      </c>
+      <c r="E82" s="5">
+        <f t="shared" si="9"/>
+        <v>115</v>
+      </c>
+      <c r="F82" s="6">
+        <f>IFERROR(B82/(B82+C82),0)</f>
+        <v>0.49101796407185627</v>
+      </c>
+      <c r="G82" s="6">
+        <f>IFERROR(B82/(B82+D82),0)</f>
+        <v>0.64566929133858264</v>
+      </c>
+      <c r="H82" s="6">
+        <f>IFERROR(2*F82*G82/(F82+G82),0)</f>
         <v>0.55782312925170074</v>
       </c>
-      <c r="I75" s="5"/>
-    </row>
-    <row r="76" spans="1:9">
-      <c r="A76" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="B76" s="7">
+      <c r="I82" s="5"/>
+    </row>
+    <row r="83" spans="1:9">
+      <c r="A83" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B83" s="7">
         <v>84</v>
       </c>
-      <c r="C76" s="7">
+      <c r="C83" s="7">
         <v>88</v>
       </c>
-      <c r="D76" s="7">
+      <c r="D83" s="7">
         <v>43</v>
       </c>
-      <c r="E76" s="7">
-        <f t="shared" si="8"/>
+      <c r="E83" s="7">
+        <f t="shared" si="9"/>
         <v>112</v>
       </c>
-      <c r="F76" s="8">
-        <f>IFERROR(B76/(B76+C76),0)</f>
+      <c r="F83" s="8">
+        <f>IFERROR(B83/(B83+C83),0)</f>
         <v>0.48837209302325579</v>
       </c>
-      <c r="G76" s="8">
-        <f>IFERROR(B76/(B76+D76),0)</f>
+      <c r="G83" s="8">
+        <f>IFERROR(B83/(B83+D83),0)</f>
         <v>0.66141732283464572</v>
       </c>
-      <c r="H76" s="8">
-        <f>IFERROR(2*F76*G76/(F76+G76),0)</f>
+      <c r="H83" s="8">
+        <f>IFERROR(2*F83*G83/(F83+G83),0)</f>
         <v>0.56187290969899661</v>
       </c>
-      <c r="I76" s="5"/>
-    </row>
-    <row r="77" spans="1:9">
-      <c r="A77" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="B77" s="10">
-        <f>AVERAGE(B72,B73,B74,B75,B76)</f>
+      <c r="I83" s="5"/>
+    </row>
+    <row r="84" spans="1:9">
+      <c r="A84" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="B84" s="10">
+        <f>AVERAGE(B79,B80,B81,B82,B83)</f>
         <v>75.400000000000006</v>
       </c>
-      <c r="C77" s="10">
-        <f>AVERAGE(C72,C73,C74,C75,C76)</f>
+      <c r="C84" s="10">
+        <f>AVERAGE(C79,C80,C81,C82,C83)</f>
         <v>82</v>
       </c>
-      <c r="D77" s="10">
-        <f>AVERAGE(D72,D73,D74,D75,D76)</f>
+      <c r="D84" s="10">
+        <f>AVERAGE(D79,D80,D81,D82,D83)</f>
         <v>51.6</v>
       </c>
-      <c r="E77" s="10">
-        <f t="shared" si="8"/>
+      <c r="E84" s="10">
+        <f t="shared" si="9"/>
         <v>118</v>
       </c>
-      <c r="F77" s="11">
-        <f>AVERAGE(F72,F73,F74,F75,F76)</f>
+      <c r="F84" s="11">
+        <f>AVERAGE(F79,F80,F81,F82,F83)</f>
         <v>0.48017502957661023</v>
       </c>
-      <c r="G77" s="11">
-        <f>AVERAGE(G72,G73,G74,G75,G76)</f>
+      <c r="G84" s="11">
+        <f>AVERAGE(G79,G80,G81,G82,G83)</f>
         <v>0.59370078740157484</v>
       </c>
-      <c r="H77" s="11">
-        <f>AVERAGE(H72,H73,H74,H75,H76)</f>
+      <c r="H84" s="11">
+        <f>AVERAGE(H79,H80,H81,H82,H83)</f>
         <v>0.52325459704167843</v>
       </c>
-      <c r="I77" s="9"/>
+      <c r="I84" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -3659,136 +3931,136 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>309</v>
+        <v>330</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
       <c r="A2" s="12" t="s">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>313</v>
+        <v>334</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1">
       <c r="A3" s="12" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>316</v>
+        <v>337</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>320</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1">
       <c r="A5" s="12" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>322</v>
+        <v>343</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1">
       <c r="A6" s="14" t="s">
-        <v>324</v>
+        <v>345</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>325</v>
+        <v>346</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>326</v>
+        <v>347</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1">
       <c r="A7" s="14" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>330</v>
+        <v>351</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>331</v>
+        <v>352</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1">
       <c r="A8" s="14" t="s">
-        <v>332</v>
+        <v>353</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>333</v>
+        <v>354</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>335</v>
+        <v>356</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1">
       <c r="A9" s="14" t="s">
-        <v>336</v>
+        <v>357</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>337</v>
+        <v>358</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>338</v>
+        <v>359</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>339</v>
+        <v>360</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1">
       <c r="A10" s="12" t="s">
-        <v>340</v>
+        <v>361</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>341</v>
+        <v>362</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>342</v>
+        <v>363</v>
       </c>
       <c r="D10" s="13"/>
     </row>
@@ -3799,7 +4071,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:A35"/>
+  <dimension ref="A1:A36"/>
   <sheetFormatPr defaultRowHeight="14.35"/>
   <cols>
     <col min="1" max="1" width="140" customWidth="1"/>
@@ -3807,147 +4079,152 @@
   <sheetData>
     <row r="1" spans="1:1" ht="16.350000000000001">
       <c r="A1" s="15" t="s">
-        <v>343</v>
+        <v>364</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="45" customHeight="1">
       <c r="A2" s="16" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="45" customHeight="1">
       <c r="A3" s="16" t="s">
-        <v>345</v>
+        <v>366</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="16.350000000000001">
       <c r="A5" s="15" t="s">
-        <v>346</v>
+        <v>367</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="45" customHeight="1">
       <c r="A6" s="16" t="s">
-        <v>347</v>
+        <v>368</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="45" customHeight="1">
       <c r="A7" s="16" t="s">
-        <v>348</v>
+        <v>369</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="45" customHeight="1">
       <c r="A8" s="16" t="s">
-        <v>349</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="45" customHeight="1">
       <c r="A9" s="16" t="s">
-        <v>350</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="45" customHeight="1">
       <c r="A10" s="16" t="s">
-        <v>351</v>
+        <v>372</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="45" customHeight="1">
       <c r="A11" s="16" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" ht="16.350000000000001">
-      <c r="A13" s="15" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" ht="45" customHeight="1">
-      <c r="A14" s="16" t="s">
-        <v>354</v>
+        <v>373</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="45" customHeight="1">
+      <c r="A12" s="16" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="16.350000000000001">
+      <c r="A14" s="15" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="45" customHeight="1">
       <c r="A15" s="16" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="45" customHeight="1">
       <c r="A16" s="16" t="s">
-        <v>356</v>
+        <v>377</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="45" customHeight="1">
       <c r="A17" s="16" t="s">
-        <v>357</v>
+        <v>378</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="45" customHeight="1">
       <c r="A18" s="16" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" ht="16.350000000000001">
-      <c r="A20" s="15" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" ht="45" customHeight="1">
-      <c r="A21" s="16" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" ht="16.350000000000001">
-      <c r="A23" s="15" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" ht="45" customHeight="1">
-      <c r="A24" s="16" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" ht="16.350000000000001">
-      <c r="A26" s="15" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" ht="45" customHeight="1">
-      <c r="A27" s="16" t="s">
-        <v>364</v>
+        <v>379</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="45" customHeight="1">
+      <c r="A19" s="16" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="16.350000000000001">
+      <c r="A21" s="15" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="45" customHeight="1">
+      <c r="A22" s="16" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="16.350000000000001">
+      <c r="A24" s="15" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="45" customHeight="1">
+      <c r="A25" s="16" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="16.350000000000001">
+      <c r="A27" s="15" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="45" customHeight="1">
       <c r="A28" s="16" t="s">
-        <v>365</v>
+        <v>386</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="45" customHeight="1">
       <c r="A29" s="16" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="45" customHeight="1">
       <c r="A30" s="16" t="s">
-        <v>367</v>
+        <v>388</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="45" customHeight="1">
       <c r="A31" s="16" t="s">
-        <v>368</v>
+        <v>389</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="45" customHeight="1">
       <c r="A32" s="16" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" ht="16.350000000000001">
-      <c r="A34" s="15" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" ht="45" customHeight="1">
-      <c r="A35" s="16" t="s">
-        <v>371</v>
+        <v>390</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" ht="45" customHeight="1">
+      <c r="A33" s="16" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" ht="16.350000000000001">
+      <c r="A35" s="15" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="45" customHeight="1">
+      <c r="A36" s="16" t="s">
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -3957,7 +4234,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:I111"/>
   <sheetFormatPr defaultRowHeight="14.35"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -3971,7 +4248,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="C1" s="18"/>
       <c r="D1" s="18"/>
@@ -4001,7 +4278,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="C3" s="18"/>
       <c r="D3" s="18"/>
@@ -4016,7 +4293,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C4" s="18"/>
       <c r="D4" s="18"/>
@@ -4031,7 +4308,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C5" s="18"/>
       <c r="D5" s="18"/>
@@ -4148,10 +4425,10 @@
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
@@ -4163,10 +4440,10 @@
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
@@ -4181,7 +4458,7 @@
         <v>21</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
@@ -4237,7 +4514,7 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="3" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -4343,7 +4620,7 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="3" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -4356,7 +4633,7 @@
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="5" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="B24" s="5">
         <v>67</v>
@@ -4387,7 +4664,7 @@
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="5" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="B25" s="5">
         <v>94</v>
@@ -4418,7 +4695,7 @@
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="5" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B26" s="5">
         <v>57</v>
@@ -4449,7 +4726,7 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="5" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="B27" s="5">
         <v>86</v>
@@ -4480,7 +4757,7 @@
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="5" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="B28" s="5">
         <v>94</v>
@@ -4511,7 +4788,7 @@
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="5" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="B29" s="5">
         <v>81</v>
@@ -4542,7 +4819,7 @@
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="5" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="B30" s="5">
         <v>57</v>
@@ -4573,7 +4850,7 @@
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="7" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="B31" s="7">
         <v>92</v>
@@ -4604,7 +4881,7 @@
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="9" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="B32" s="10">
         <f>AVERAGE(B24,B25,B26,B27,B28,B29,B30,B31)</f>
@@ -4635,12 +4912,12 @@
         <v>0.52666729935887013</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="3" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -4653,7 +4930,7 @@
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="5" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="B34" s="5">
         <v>71</v>
@@ -4684,7 +4961,7 @@
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="7" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B35" s="7">
         <v>98</v>
@@ -4715,7 +4992,7 @@
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="5" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="B36" s="5">
         <v>75</v>
@@ -4746,7 +5023,7 @@
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="5" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B37" s="5">
         <v>75</v>
@@ -4777,7 +5054,7 @@
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="5" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="B38" s="5">
         <v>88</v>
@@ -4808,7 +5085,7 @@
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="5" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="B39" s="5">
         <v>75</v>
@@ -4839,7 +5116,7 @@
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="5" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="B40" s="5">
         <v>56</v>
@@ -4870,7 +5147,7 @@
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="5" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="B41" s="5">
         <v>62</v>
@@ -4901,7 +5178,7 @@
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="9" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="B42" s="10">
         <f>AVERAGE(B34,B35,B36,B37,B38,B39,B40,B41)</f>
@@ -4932,12 +5209,12 @@
         <v>0.48869108343435741</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="3" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -4950,7 +5227,7 @@
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="5" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="B44" s="5">
         <v>58</v>
@@ -4981,7 +5258,7 @@
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="5" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="B45" s="5">
         <v>68</v>
@@ -5012,7 +5289,7 @@
     </row>
     <row r="46" spans="1:9">
       <c r="A46" s="5" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="B46" s="5">
         <v>48</v>
@@ -5043,7 +5320,7 @@
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="7" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="B47" s="7">
         <v>89</v>
@@ -5074,7 +5351,7 @@
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="5" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B48" s="5">
         <v>81</v>
@@ -5105,7 +5382,7 @@
     </row>
     <row r="49" spans="1:9">
       <c r="A49" s="5" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="B49" s="5">
         <v>86</v>
@@ -5136,7 +5413,7 @@
     </row>
     <row r="50" spans="1:9">
       <c r="A50" s="5" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="B50" s="5">
         <v>58</v>
@@ -5167,7 +5444,7 @@
     </row>
     <row r="51" spans="1:9">
       <c r="A51" s="5" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="B51" s="5">
         <v>69</v>
@@ -5198,7 +5475,7 @@
     </row>
     <row r="52" spans="1:9">
       <c r="A52" s="9" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="B52" s="10">
         <f>AVERAGE(B44,B45,B46,B47,B48,B49,B50,B51)</f>
@@ -5229,7 +5506,7 @@
         <v>0.48246608643180328</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -5275,12 +5552,12 @@
         <v>0.44979919678714864</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="55" spans="1:9">
       <c r="A55" s="5" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="B55" s="5">
         <v>69</v>
@@ -5311,7 +5588,7 @@
     </row>
     <row r="56" spans="1:9">
       <c r="A56" s="5" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="B56" s="5">
         <v>93</v>
@@ -5342,7 +5619,7 @@
     </row>
     <row r="57" spans="1:9">
       <c r="A57" s="5" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="B57" s="5">
         <v>63</v>
@@ -5373,7 +5650,7 @@
     </row>
     <row r="58" spans="1:9">
       <c r="A58" s="5" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="B58" s="5">
         <v>89</v>
@@ -5404,7 +5681,7 @@
     </row>
     <row r="59" spans="1:9">
       <c r="A59" s="7" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="B59" s="7">
         <v>96</v>
@@ -5435,7 +5712,7 @@
     </row>
     <row r="60" spans="1:9">
       <c r="A60" s="5" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B60" s="5">
         <v>88</v>
@@ -5466,7 +5743,7 @@
     </row>
     <row r="61" spans="1:9">
       <c r="A61" s="5" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="B61" s="5">
         <v>60</v>
@@ -5497,7 +5774,7 @@
     </row>
     <row r="62" spans="1:9">
       <c r="A62" s="5" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B62" s="5">
         <v>81</v>
@@ -5528,7 +5805,7 @@
     </row>
     <row r="63" spans="1:9">
       <c r="A63" s="9" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B63" s="10">
         <f>AVERAGE(B55,B56,B57,B58,B59,B60,B61,B62)</f>
@@ -5564,7 +5841,7 @@
     </row>
     <row r="64" spans="1:9">
       <c r="A64" s="3" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -5577,7 +5854,7 @@
     </row>
     <row r="65" spans="1:9">
       <c r="A65" s="5" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B65" s="5">
         <v>82</v>
@@ -5605,12 +5882,12 @@
         <v>0.53770491803278686</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="7" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B66" s="7">
         <v>99</v>
@@ -5641,7 +5918,7 @@
     </row>
     <row r="67" spans="1:9">
       <c r="A67" s="5" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="B67" s="5">
         <v>82</v>
@@ -5672,7 +5949,7 @@
     </row>
     <row r="68" spans="1:9">
       <c r="A68" s="5" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="B68" s="5">
         <v>90</v>
@@ -5703,7 +5980,7 @@
     </row>
     <row r="69" spans="1:9">
       <c r="A69" s="5" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="B69" s="5">
         <v>97</v>
@@ -5734,7 +6011,7 @@
     </row>
     <row r="70" spans="1:9">
       <c r="A70" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B70" s="5">
         <v>83</v>
@@ -5765,7 +6042,7 @@
     </row>
     <row r="71" spans="1:9">
       <c r="A71" s="5" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B71" s="5">
         <v>70</v>
@@ -5796,7 +6073,7 @@
     </row>
     <row r="72" spans="1:9">
       <c r="A72" s="5" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="B72" s="5">
         <v>86</v>
@@ -5827,7 +6104,7 @@
     </row>
     <row r="73" spans="1:9">
       <c r="A73" s="9" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B73" s="10">
         <f>AVERAGE(B65,B66,B67,B68,B69,B70,B71,B72)</f>
@@ -5861,7 +6138,7 @@
     </row>
     <row r="74" spans="1:9">
       <c r="A74" s="5" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="B74" s="5">
         <v>99</v>
@@ -5889,12 +6166,12 @@
         <v>0.52800000000000002</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
     </row>
     <row r="75" spans="1:9">
       <c r="A75" s="5" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="B75" s="5">
         <v>110</v>
@@ -5925,7 +6202,7 @@
     </row>
     <row r="76" spans="1:9">
       <c r="A76" s="5" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="B76" s="5">
         <v>102</v>
@@ -5956,7 +6233,7 @@
     </row>
     <row r="77" spans="1:9">
       <c r="A77" s="7" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="B77" s="7">
         <v>109</v>
@@ -5987,7 +6264,7 @@
     </row>
     <row r="78" spans="1:9">
       <c r="A78" s="5" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="B78" s="5">
         <v>109</v>
@@ -6018,7 +6295,7 @@
     </row>
     <row r="79" spans="1:9">
       <c r="A79" s="5" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B79" s="5">
         <v>105</v>
@@ -6049,7 +6326,7 @@
     </row>
     <row r="80" spans="1:9">
       <c r="A80" s="5" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B80" s="5">
         <v>99</v>
@@ -6080,7 +6357,7 @@
     </row>
     <row r="81" spans="1:9">
       <c r="A81" s="5" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B81" s="5">
         <v>105</v>
@@ -6111,7 +6388,7 @@
     </row>
     <row r="82" spans="1:9">
       <c r="A82" s="9" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="B82" s="10">
         <f>AVERAGE(B74,B75,B76,B77,B78,B79,B80,B81)</f>
@@ -6142,7 +6419,7 @@
         <v>0.54938867470744024</v>
       </c>
       <c r="I82" s="9" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -6160,567 +6437,866 @@
     </row>
     <row r="84" spans="1:9">
       <c r="A84" s="5" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="B84" s="5">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C84" s="5">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="D84" s="5">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E84" s="5">
-        <f t="shared" ref="E84:E101" si="23">327-B84-C84-D84</f>
-        <v>72</v>
+        <f t="shared" ref="E84:E92" si="23">327-B84-C84-D84</f>
+        <v>62</v>
       </c>
       <c r="F84" s="6">
         <f t="shared" ref="F84:F91" si="24">IFERROR(B84/(B84+C84),0)</f>
-        <v>0.43612334801762115</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G84" s="6">
         <f t="shared" ref="G84:G91" si="25">IFERROR(B84/(B84+D84),0)</f>
-        <v>0.77952755905511806</v>
+        <v>0.80314960629921262</v>
       </c>
       <c r="H84" s="6">
         <f t="shared" ref="H84:H91" si="26">IFERROR(2*F84*G84/(F84+G84),0)</f>
-        <v>0.55932203389830504</v>
-      </c>
-      <c r="I84" s="5"/>
+        <v>0.55585831062670299</v>
+      </c>
+      <c r="I84" s="5" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="85" spans="1:9">
-      <c r="A85" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="B85" s="7">
+      <c r="A85" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="B85" s="5">
+        <v>109</v>
+      </c>
+      <c r="C85" s="5">
+        <v>146</v>
+      </c>
+      <c r="D85" s="5">
+        <v>18</v>
+      </c>
+      <c r="E85" s="5">
+        <f t="shared" si="23"/>
+        <v>54</v>
+      </c>
+      <c r="F85" s="6">
+        <f t="shared" si="24"/>
+        <v>0.42745098039215684</v>
+      </c>
+      <c r="G85" s="6">
+        <f t="shared" si="25"/>
+        <v>0.8582677165354331</v>
+      </c>
+      <c r="H85" s="6">
+        <f t="shared" si="26"/>
+        <v>0.5706806282722513</v>
+      </c>
+      <c r="I85" s="5"/>
+    </row>
+    <row r="86" spans="1:9">
+      <c r="A86" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B86" s="5">
+        <v>105</v>
+      </c>
+      <c r="C86" s="5">
+        <v>136</v>
+      </c>
+      <c r="D86" s="5">
+        <v>22</v>
+      </c>
+      <c r="E86" s="5">
+        <f t="shared" si="23"/>
+        <v>64</v>
+      </c>
+      <c r="F86" s="6">
+        <f t="shared" si="24"/>
+        <v>0.43568464730290457</v>
+      </c>
+      <c r="G86" s="6">
+        <f t="shared" si="25"/>
+        <v>0.82677165354330706</v>
+      </c>
+      <c r="H86" s="6">
+        <f t="shared" si="26"/>
+        <v>0.57065217391304346</v>
+      </c>
+      <c r="I86" s="5"/>
+    </row>
+    <row r="87" spans="1:9">
+      <c r="A87" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="B87" s="7">
+        <v>115</v>
+      </c>
+      <c r="C87" s="7">
+        <v>155</v>
+      </c>
+      <c r="D87" s="7">
+        <v>12</v>
+      </c>
+      <c r="E87" s="7">
+        <f t="shared" si="23"/>
+        <v>45</v>
+      </c>
+      <c r="F87" s="8">
+        <f t="shared" si="24"/>
+        <v>0.42592592592592593</v>
+      </c>
+      <c r="G87" s="8">
+        <f t="shared" si="25"/>
+        <v>0.90551181102362199</v>
+      </c>
+      <c r="H87" s="8">
+        <f t="shared" si="26"/>
+        <v>0.57934508816120911</v>
+      </c>
+      <c r="I87" s="5"/>
+    </row>
+    <row r="88" spans="1:9">
+      <c r="A88" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B88" s="5">
+        <v>110</v>
+      </c>
+      <c r="C88" s="5">
+        <v>152</v>
+      </c>
+      <c r="D88" s="5">
+        <v>17</v>
+      </c>
+      <c r="E88" s="5">
+        <f t="shared" si="23"/>
+        <v>48</v>
+      </c>
+      <c r="F88" s="6">
+        <f t="shared" si="24"/>
+        <v>0.41984732824427479</v>
+      </c>
+      <c r="G88" s="6">
+        <f t="shared" si="25"/>
+        <v>0.86614173228346458</v>
+      </c>
+      <c r="H88" s="6">
+        <f t="shared" si="26"/>
+        <v>0.56555269922879181</v>
+      </c>
+      <c r="I88" s="5"/>
+    </row>
+    <row r="89" spans="1:9">
+      <c r="A89" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B89" s="5">
+        <v>113</v>
+      </c>
+      <c r="C89" s="5">
+        <v>154</v>
+      </c>
+      <c r="D89" s="5">
+        <v>14</v>
+      </c>
+      <c r="E89" s="5">
+        <f t="shared" si="23"/>
+        <v>46</v>
+      </c>
+      <c r="F89" s="6">
+        <f t="shared" si="24"/>
+        <v>0.42322097378277151</v>
+      </c>
+      <c r="G89" s="6">
+        <f t="shared" si="25"/>
+        <v>0.88976377952755903</v>
+      </c>
+      <c r="H89" s="6">
+        <f t="shared" si="26"/>
+        <v>0.57360406091370564</v>
+      </c>
+      <c r="I89" s="5"/>
+    </row>
+    <row r="90" spans="1:9">
+      <c r="A90" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B90" s="5">
+        <v>103</v>
+      </c>
+      <c r="C90" s="5">
+        <v>144</v>
+      </c>
+      <c r="D90" s="5">
+        <v>24</v>
+      </c>
+      <c r="E90" s="5">
+        <f t="shared" si="23"/>
+        <v>56</v>
+      </c>
+      <c r="F90" s="6">
+        <f t="shared" si="24"/>
+        <v>0.41700404858299595</v>
+      </c>
+      <c r="G90" s="6">
+        <f t="shared" si="25"/>
+        <v>0.8110236220472441</v>
+      </c>
+      <c r="H90" s="6">
+        <f t="shared" si="26"/>
+        <v>0.55080213903743314</v>
+      </c>
+      <c r="I90" s="5"/>
+    </row>
+    <row r="91" spans="1:9">
+      <c r="A91" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B91" s="5">
         <v>108</v>
       </c>
-      <c r="C85" s="7">
-        <v>141</v>
-      </c>
-      <c r="D85" s="7">
+      <c r="C91" s="5">
+        <v>148</v>
+      </c>
+      <c r="D91" s="5">
         <v>19</v>
       </c>
-      <c r="E85" s="7">
+      <c r="E91" s="5">
         <f t="shared" si="23"/>
-        <v>59</v>
-      </c>
-      <c r="F85" s="8">
+        <v>52</v>
+      </c>
+      <c r="F91" s="6">
         <f t="shared" si="24"/>
-        <v>0.43373493975903615</v>
-      </c>
-      <c r="G85" s="8">
+        <v>0.421875</v>
+      </c>
+      <c r="G91" s="6">
         <f t="shared" si="25"/>
         <v>0.85039370078740162</v>
       </c>
-      <c r="H85" s="8">
-        <f t="shared" si="26"/>
-        <v>0.57446808510638303</v>
-      </c>
-      <c r="I85" s="5"/>
-    </row>
-    <row r="86" spans="1:9">
-      <c r="A86" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="B86" s="5">
-        <v>100</v>
-      </c>
-      <c r="C86" s="5">
-        <v>134</v>
-      </c>
-      <c r="D86" s="5">
-        <v>27</v>
-      </c>
-      <c r="E86" s="5">
-        <f t="shared" si="23"/>
-        <v>66</v>
-      </c>
-      <c r="F86" s="6">
-        <f t="shared" si="24"/>
-        <v>0.42735042735042733</v>
-      </c>
-      <c r="G86" s="6">
-        <f t="shared" si="25"/>
-        <v>0.78740157480314965</v>
-      </c>
-      <c r="H86" s="6">
-        <f t="shared" si="26"/>
-        <v>0.554016620498615</v>
-      </c>
-      <c r="I86" s="5"/>
-    </row>
-    <row r="87" spans="1:9">
-      <c r="A87" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="B87" s="5">
-        <v>108</v>
-      </c>
-      <c r="C87" s="5">
-        <v>146</v>
-      </c>
-      <c r="D87" s="5">
-        <v>19</v>
-      </c>
-      <c r="E87" s="5">
-        <f t="shared" si="23"/>
-        <v>54</v>
-      </c>
-      <c r="F87" s="6">
-        <f t="shared" si="24"/>
-        <v>0.42519685039370081</v>
-      </c>
-      <c r="G87" s="6">
-        <f t="shared" si="25"/>
-        <v>0.85039370078740162</v>
-      </c>
-      <c r="H87" s="6">
-        <f t="shared" si="26"/>
-        <v>0.56692913385826782</v>
-      </c>
-      <c r="I87" s="5"/>
-    </row>
-    <row r="88" spans="1:9">
-      <c r="A88" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="B88" s="5">
-        <v>107</v>
-      </c>
-      <c r="C88" s="5">
-        <v>149</v>
-      </c>
-      <c r="D88" s="5">
-        <v>20</v>
-      </c>
-      <c r="E88" s="5">
-        <f t="shared" si="23"/>
-        <v>51</v>
-      </c>
-      <c r="F88" s="6">
-        <f t="shared" si="24"/>
-        <v>0.41796875</v>
-      </c>
-      <c r="G88" s="6">
-        <f t="shared" si="25"/>
-        <v>0.84251968503937003</v>
-      </c>
-      <c r="H88" s="6">
-        <f t="shared" si="26"/>
-        <v>0.55874673629242821</v>
-      </c>
-      <c r="I88" s="5"/>
-    </row>
-    <row r="89" spans="1:9">
-      <c r="A89" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="B89" s="5">
-        <v>105</v>
-      </c>
-      <c r="C89" s="5">
-        <v>136</v>
-      </c>
-      <c r="D89" s="5">
-        <v>22</v>
-      </c>
-      <c r="E89" s="5">
-        <f t="shared" si="23"/>
-        <v>64</v>
-      </c>
-      <c r="F89" s="6">
-        <f t="shared" si="24"/>
-        <v>0.43568464730290457</v>
-      </c>
-      <c r="G89" s="6">
-        <f t="shared" si="25"/>
-        <v>0.82677165354330706</v>
-      </c>
-      <c r="H89" s="6">
-        <f t="shared" si="26"/>
-        <v>0.57065217391304346</v>
-      </c>
-      <c r="I89" s="5"/>
-    </row>
-    <row r="90" spans="1:9">
-      <c r="A90" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="B90" s="5">
-        <v>98</v>
-      </c>
-      <c r="C90" s="5">
-        <v>132</v>
-      </c>
-      <c r="D90" s="5">
-        <v>29</v>
-      </c>
-      <c r="E90" s="5">
-        <f t="shared" si="23"/>
-        <v>68</v>
-      </c>
-      <c r="F90" s="6">
-        <f t="shared" si="24"/>
-        <v>0.42608695652173911</v>
-      </c>
-      <c r="G90" s="6">
-        <f t="shared" si="25"/>
-        <v>0.77165354330708658</v>
-      </c>
-      <c r="H90" s="6">
-        <f t="shared" si="26"/>
-        <v>0.5490196078431373</v>
-      </c>
-      <c r="I90" s="5"/>
-    </row>
-    <row r="91" spans="1:9">
-      <c r="A91" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="B91" s="5">
-        <v>105</v>
-      </c>
-      <c r="C91" s="5">
-        <v>141</v>
-      </c>
-      <c r="D91" s="5">
-        <v>22</v>
-      </c>
-      <c r="E91" s="5">
-        <f t="shared" si="23"/>
-        <v>59</v>
-      </c>
-      <c r="F91" s="6">
-        <f t="shared" si="24"/>
-        <v>0.42682926829268292</v>
-      </c>
-      <c r="G91" s="6">
-        <f t="shared" si="25"/>
-        <v>0.82677165354330706</v>
-      </c>
       <c r="H91" s="6">
         <f t="shared" si="26"/>
-        <v>0.56300268096514738</v>
+        <v>0.56396866840731075</v>
       </c>
       <c r="I91" s="5"/>
     </row>
     <row r="92" spans="1:9">
       <c r="A92" s="9" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="B92" s="10">
         <f>AVERAGE(B84,B85,B86,B87,B88,B89,B90,B91)</f>
-        <v>103.75</v>
+        <v>108.125</v>
       </c>
       <c r="C92" s="10">
         <f>AVERAGE(C84,C85,C86,C87,C88,C89,C90,C91)</f>
-        <v>138.375</v>
+        <v>146.625</v>
       </c>
       <c r="D92" s="10">
         <f>AVERAGE(D84,D85,D86,D87,D88,D89,D90,D91)</f>
-        <v>23.25</v>
+        <v>18.875</v>
       </c>
       <c r="E92" s="10">
         <f t="shared" si="23"/>
-        <v>61.625</v>
+        <v>53.375</v>
       </c>
       <c r="F92" s="11">
         <f>AVERAGE(F84,F85,F86,F87,F88,F89,F90,F91)</f>
-        <v>0.42862189845476395</v>
+        <v>0.42450111302887866</v>
       </c>
       <c r="G92" s="11">
         <f>AVERAGE(G84,G85,G86,G87,G88,G89,G90,G91)</f>
-        <v>0.81692913385826782</v>
+        <v>0.85137795275590566</v>
       </c>
       <c r="H92" s="11">
         <f>AVERAGE(H84,H85,H86,H87,H88,H89,H90,H91)</f>
-        <v>0.56201963404691591</v>
-      </c>
-      <c r="I92" s="9"/>
+        <v>0.56630797107005604</v>
+      </c>
+      <c r="I92" s="9" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="93" spans="1:9">
-      <c r="A93" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="B93" s="5">
-        <v>61</v>
-      </c>
-      <c r="C93" s="5">
-        <v>57</v>
-      </c>
-      <c r="D93" s="5">
-        <v>66</v>
-      </c>
-      <c r="E93" s="5">
-        <f t="shared" si="23"/>
-        <v>143</v>
-      </c>
-      <c r="F93" s="6">
-        <f t="shared" ref="F93:F100" si="27">IFERROR(B93/(B93+C93),0)</f>
-        <v>0.51694915254237284</v>
-      </c>
-      <c r="G93" s="6">
-        <f t="shared" ref="G93:G100" si="28">IFERROR(B93/(B93+D93),0)</f>
-        <v>0.48031496062992124</v>
-      </c>
-      <c r="H93" s="6">
-        <f t="shared" ref="H93:H100" si="29">IFERROR(2*F93*G93/(F93+G93),0)</f>
-        <v>0.49795918367346936</v>
-      </c>
-      <c r="I93" s="5"/>
+      <c r="A93" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B93" s="4"/>
+      <c r="C93" s="4"/>
+      <c r="D93" s="4"/>
+      <c r="E93" s="4"/>
+      <c r="F93" s="4"/>
+      <c r="G93" s="4"/>
+      <c r="H93" s="4"/>
+      <c r="I93" s="4"/>
     </row>
     <row r="94" spans="1:9">
       <c r="A94" s="5" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B94" s="5">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="C94" s="5">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="D94" s="5">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="E94" s="5">
-        <f t="shared" si="23"/>
-        <v>121</v>
+        <f t="shared" ref="E94:E111" si="27">327-B94-C94-D94</f>
+        <v>72</v>
       </c>
       <c r="F94" s="6">
+        <f t="shared" ref="F94:F101" si="28">IFERROR(B94/(B94+C94),0)</f>
+        <v>0.43612334801762115</v>
+      </c>
+      <c r="G94" s="6">
+        <f t="shared" ref="G94:G101" si="29">IFERROR(B94/(B94+D94),0)</f>
+        <v>0.77952755905511806</v>
+      </c>
+      <c r="H94" s="6">
+        <f t="shared" ref="H94:H101" si="30">IFERROR(2*F94*G94/(F94+G94),0)</f>
+        <v>0.55932203389830504</v>
+      </c>
+      <c r="I94" s="5"/>
+    </row>
+    <row r="95" spans="1:9">
+      <c r="A95" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="B95" s="7">
+        <v>108</v>
+      </c>
+      <c r="C95" s="7">
+        <v>141</v>
+      </c>
+      <c r="D95" s="7">
+        <v>19</v>
+      </c>
+      <c r="E95" s="7">
         <f t="shared" si="27"/>
-        <v>0.5</v>
-      </c>
-      <c r="G94" s="6">
+        <v>59</v>
+      </c>
+      <c r="F95" s="8">
         <f t="shared" si="28"/>
-        <v>0.62204724409448819</v>
-      </c>
-      <c r="H94" s="6">
+        <v>0.43373493975903615</v>
+      </c>
+      <c r="G95" s="8">
         <f t="shared" si="29"/>
-        <v>0.55438596491228065</v>
-      </c>
-      <c r="I94" s="5"/>
-    </row>
-    <row r="95" spans="1:9">
-      <c r="A95" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="B95" s="5">
-        <v>50</v>
-      </c>
-      <c r="C95" s="5">
-        <v>53</v>
-      </c>
-      <c r="D95" s="5">
-        <v>77</v>
-      </c>
-      <c r="E95" s="5">
-        <f t="shared" si="23"/>
-        <v>147</v>
-      </c>
-      <c r="F95" s="6">
-        <f t="shared" si="27"/>
-        <v>0.4854368932038835</v>
-      </c>
-      <c r="G95" s="6">
-        <f t="shared" si="28"/>
-        <v>0.39370078740157483</v>
-      </c>
-      <c r="H95" s="6">
-        <f t="shared" si="29"/>
-        <v>0.43478260869565222</v>
+        <v>0.85039370078740162</v>
+      </c>
+      <c r="H95" s="8">
+        <f t="shared" si="30"/>
+        <v>0.57446808510638303</v>
       </c>
       <c r="I95" s="5"/>
     </row>
     <row r="96" spans="1:9">
       <c r="A96" s="5" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="B96" s="5">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="C96" s="5">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="D96" s="5">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="E96" s="5">
-        <f t="shared" si="23"/>
-        <v>121</v>
+        <f t="shared" si="27"/>
+        <v>66</v>
       </c>
       <c r="F96" s="6">
-        <f t="shared" si="27"/>
-        <v>0.47333333333333333</v>
+        <f t="shared" si="28"/>
+        <v>0.42735042735042733</v>
       </c>
       <c r="G96" s="6">
-        <f t="shared" si="28"/>
-        <v>0.55905511811023623</v>
+        <f t="shared" si="29"/>
+        <v>0.78740157480314965</v>
       </c>
       <c r="H96" s="6">
-        <f t="shared" si="29"/>
-        <v>0.5126353790613718</v>
+        <f t="shared" si="30"/>
+        <v>0.554016620498615</v>
       </c>
       <c r="I96" s="5"/>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="5" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="B97" s="5">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="C97" s="5">
-        <v>89</v>
+        <v>146</v>
       </c>
       <c r="D97" s="5">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="E97" s="5">
-        <f t="shared" si="23"/>
-        <v>111</v>
+        <f t="shared" si="27"/>
+        <v>54</v>
       </c>
       <c r="F97" s="6">
-        <f t="shared" si="27"/>
-        <v>0.47337278106508873</v>
+        <f t="shared" si="28"/>
+        <v>0.42519685039370081</v>
       </c>
       <c r="G97" s="6">
-        <f t="shared" si="28"/>
-        <v>0.62992125984251968</v>
+        <f t="shared" si="29"/>
+        <v>0.85039370078740162</v>
       </c>
       <c r="H97" s="6">
-        <f t="shared" si="29"/>
-        <v>0.54054054054054057</v>
+        <f t="shared" si="30"/>
+        <v>0.56692913385826782</v>
       </c>
       <c r="I97" s="5"/>
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="5" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="B98" s="5">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="C98" s="5">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="D98" s="5">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="E98" s="5">
-        <f t="shared" si="23"/>
-        <v>123</v>
+        <f t="shared" si="27"/>
+        <v>51</v>
       </c>
       <c r="F98" s="6">
-        <f t="shared" si="27"/>
-        <v>0.4726027397260274</v>
+        <f t="shared" si="28"/>
+        <v>0.41796875</v>
       </c>
       <c r="G98" s="6">
-        <f t="shared" si="28"/>
-        <v>0.54330708661417326</v>
+        <f t="shared" si="29"/>
+        <v>0.84251968503937003</v>
       </c>
       <c r="H98" s="6">
-        <f t="shared" si="29"/>
-        <v>0.50549450549450547</v>
+        <f t="shared" si="30"/>
+        <v>0.55874673629242821</v>
       </c>
       <c r="I98" s="5"/>
     </row>
     <row r="99" spans="1:9">
       <c r="A99" s="5" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="B99" s="5">
+        <v>105</v>
+      </c>
+      <c r="C99" s="5">
+        <v>136</v>
+      </c>
+      <c r="D99" s="5">
+        <v>22</v>
+      </c>
+      <c r="E99" s="5">
+        <f t="shared" si="27"/>
+        <v>64</v>
+      </c>
+      <c r="F99" s="6">
+        <f t="shared" si="28"/>
+        <v>0.43568464730290457</v>
+      </c>
+      <c r="G99" s="6">
+        <f t="shared" si="29"/>
+        <v>0.82677165354330706</v>
+      </c>
+      <c r="H99" s="6">
+        <f t="shared" si="30"/>
+        <v>0.57065217391304346</v>
+      </c>
+      <c r="I99" s="5"/>
+    </row>
+    <row r="100" spans="1:9">
+      <c r="A100" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B100" s="5">
+        <v>98</v>
+      </c>
+      <c r="C100" s="5">
+        <v>132</v>
+      </c>
+      <c r="D100" s="5">
+        <v>29</v>
+      </c>
+      <c r="E100" s="5">
+        <f t="shared" si="27"/>
+        <v>68</v>
+      </c>
+      <c r="F100" s="6">
+        <f t="shared" si="28"/>
+        <v>0.42608695652173911</v>
+      </c>
+      <c r="G100" s="6">
+        <f t="shared" si="29"/>
+        <v>0.77165354330708658</v>
+      </c>
+      <c r="H100" s="6">
+        <f t="shared" si="30"/>
+        <v>0.5490196078431373</v>
+      </c>
+      <c r="I100" s="5"/>
+    </row>
+    <row r="101" spans="1:9">
+      <c r="A101" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="B101" s="5">
+        <v>105</v>
+      </c>
+      <c r="C101" s="5">
+        <v>141</v>
+      </c>
+      <c r="D101" s="5">
+        <v>22</v>
+      </c>
+      <c r="E101" s="5">
+        <f t="shared" si="27"/>
+        <v>59</v>
+      </c>
+      <c r="F101" s="6">
+        <f t="shared" si="28"/>
+        <v>0.42682926829268292</v>
+      </c>
+      <c r="G101" s="6">
+        <f t="shared" si="29"/>
+        <v>0.82677165354330706</v>
+      </c>
+      <c r="H101" s="6">
+        <f t="shared" si="30"/>
+        <v>0.56300268096514738</v>
+      </c>
+      <c r="I101" s="5"/>
+    </row>
+    <row r="102" spans="1:9">
+      <c r="A102" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="B102" s="10">
+        <f>AVERAGE(B94,B95,B96,B97,B98,B99,B100,B101)</f>
+        <v>103.75</v>
+      </c>
+      <c r="C102" s="10">
+        <f>AVERAGE(C94,C95,C96,C97,C98,C99,C100,C101)</f>
+        <v>138.375</v>
+      </c>
+      <c r="D102" s="10">
+        <f>AVERAGE(D94,D95,D96,D97,D98,D99,D100,D101)</f>
+        <v>23.25</v>
+      </c>
+      <c r="E102" s="10">
+        <f t="shared" si="27"/>
+        <v>61.625</v>
+      </c>
+      <c r="F102" s="11">
+        <f>AVERAGE(F94,F95,F96,F97,F98,F99,F100,F101)</f>
+        <v>0.42862189845476395</v>
+      </c>
+      <c r="G102" s="11">
+        <f>AVERAGE(G94,G95,G96,G97,G98,G99,G100,G101)</f>
+        <v>0.81692913385826782</v>
+      </c>
+      <c r="H102" s="11">
+        <f>AVERAGE(H94,H95,H96,H97,H98,H99,H100,H101)</f>
+        <v>0.56201963404691591</v>
+      </c>
+      <c r="I102" s="9"/>
+    </row>
+    <row r="103" spans="1:9">
+      <c r="A103" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="B103" s="5">
+        <v>61</v>
+      </c>
+      <c r="C103" s="5">
+        <v>57</v>
+      </c>
+      <c r="D103" s="5">
+        <v>66</v>
+      </c>
+      <c r="E103" s="5">
+        <f t="shared" si="27"/>
+        <v>143</v>
+      </c>
+      <c r="F103" s="6">
+        <f t="shared" ref="F103:F110" si="31">IFERROR(B103/(B103+C103),0)</f>
+        <v>0.51694915254237284</v>
+      </c>
+      <c r="G103" s="6">
+        <f t="shared" ref="G103:G110" si="32">IFERROR(B103/(B103+D103),0)</f>
+        <v>0.48031496062992124</v>
+      </c>
+      <c r="H103" s="6">
+        <f t="shared" ref="H103:H110" si="33">IFERROR(2*F103*G103/(F103+G103),0)</f>
+        <v>0.49795918367346936</v>
+      </c>
+      <c r="I103" s="5"/>
+    </row>
+    <row r="104" spans="1:9">
+      <c r="A104" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="B104" s="5">
+        <v>79</v>
+      </c>
+      <c r="C104" s="5">
+        <v>79</v>
+      </c>
+      <c r="D104" s="5">
+        <v>48</v>
+      </c>
+      <c r="E104" s="5">
+        <f t="shared" si="27"/>
+        <v>121</v>
+      </c>
+      <c r="F104" s="6">
+        <f t="shared" si="31"/>
+        <v>0.5</v>
+      </c>
+      <c r="G104" s="6">
+        <f t="shared" si="32"/>
+        <v>0.62204724409448819</v>
+      </c>
+      <c r="H104" s="6">
+        <f t="shared" si="33"/>
+        <v>0.55438596491228065</v>
+      </c>
+      <c r="I104" s="5"/>
+    </row>
+    <row r="105" spans="1:9">
+      <c r="A105" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B105" s="5">
+        <v>50</v>
+      </c>
+      <c r="C105" s="5">
+        <v>53</v>
+      </c>
+      <c r="D105" s="5">
+        <v>77</v>
+      </c>
+      <c r="E105" s="5">
+        <f t="shared" si="27"/>
+        <v>147</v>
+      </c>
+      <c r="F105" s="6">
+        <f t="shared" si="31"/>
+        <v>0.4854368932038835</v>
+      </c>
+      <c r="G105" s="6">
+        <f t="shared" si="32"/>
+        <v>0.39370078740157483</v>
+      </c>
+      <c r="H105" s="6">
+        <f t="shared" si="33"/>
+        <v>0.43478260869565222</v>
+      </c>
+      <c r="I105" s="5"/>
+    </row>
+    <row r="106" spans="1:9">
+      <c r="A106" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B106" s="5">
+        <v>71</v>
+      </c>
+      <c r="C106" s="5">
+        <v>79</v>
+      </c>
+      <c r="D106" s="5">
+        <v>56</v>
+      </c>
+      <c r="E106" s="5">
+        <f t="shared" si="27"/>
+        <v>121</v>
+      </c>
+      <c r="F106" s="6">
+        <f t="shared" si="31"/>
+        <v>0.47333333333333333</v>
+      </c>
+      <c r="G106" s="6">
+        <f t="shared" si="32"/>
+        <v>0.55905511811023623</v>
+      </c>
+      <c r="H106" s="6">
+        <f t="shared" si="33"/>
+        <v>0.5126353790613718</v>
+      </c>
+      <c r="I106" s="5"/>
+    </row>
+    <row r="107" spans="1:9">
+      <c r="A107" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="B107" s="5">
+        <v>80</v>
+      </c>
+      <c r="C107" s="5">
+        <v>89</v>
+      </c>
+      <c r="D107" s="5">
+        <v>47</v>
+      </c>
+      <c r="E107" s="5">
+        <f t="shared" si="27"/>
+        <v>111</v>
+      </c>
+      <c r="F107" s="6">
+        <f t="shared" si="31"/>
+        <v>0.47337278106508873</v>
+      </c>
+      <c r="G107" s="6">
+        <f t="shared" si="32"/>
+        <v>0.62992125984251968</v>
+      </c>
+      <c r="H107" s="6">
+        <f t="shared" si="33"/>
+        <v>0.54054054054054057</v>
+      </c>
+      <c r="I107" s="5"/>
+    </row>
+    <row r="108" spans="1:9">
+      <c r="A108" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B108" s="5">
+        <v>69</v>
+      </c>
+      <c r="C108" s="5">
+        <v>77</v>
+      </c>
+      <c r="D108" s="5">
+        <v>58</v>
+      </c>
+      <c r="E108" s="5">
+        <f t="shared" si="27"/>
+        <v>123</v>
+      </c>
+      <c r="F108" s="6">
+        <f t="shared" si="31"/>
+        <v>0.4726027397260274</v>
+      </c>
+      <c r="G108" s="6">
+        <f t="shared" si="32"/>
+        <v>0.54330708661417326</v>
+      </c>
+      <c r="H108" s="6">
+        <f t="shared" si="33"/>
+        <v>0.50549450549450547</v>
+      </c>
+      <c r="I108" s="5"/>
+    </row>
+    <row r="109" spans="1:9">
+      <c r="A109" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="B109" s="5">
         <v>52</v>
       </c>
-      <c r="C99" s="5">
+      <c r="C109" s="5">
         <v>59</v>
       </c>
-      <c r="D99" s="5">
+      <c r="D109" s="5">
         <v>75</v>
       </c>
-      <c r="E99" s="5">
-        <f t="shared" si="23"/>
+      <c r="E109" s="5">
+        <f t="shared" si="27"/>
         <v>141</v>
       </c>
-      <c r="F99" s="6">
+      <c r="F109" s="6">
+        <f t="shared" si="31"/>
+        <v>0.46846846846846846</v>
+      </c>
+      <c r="G109" s="6">
+        <f t="shared" si="32"/>
+        <v>0.40944881889763779</v>
+      </c>
+      <c r="H109" s="6">
+        <f t="shared" si="33"/>
+        <v>0.43697478991596633</v>
+      </c>
+      <c r="I109" s="5"/>
+    </row>
+    <row r="110" spans="1:9">
+      <c r="A110" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="B110" s="7">
+        <v>80</v>
+      </c>
+      <c r="C110" s="7">
+        <v>72</v>
+      </c>
+      <c r="D110" s="7">
+        <v>47</v>
+      </c>
+      <c r="E110" s="7">
         <f t="shared" si="27"/>
-        <v>0.46846846846846846</v>
-      </c>
-      <c r="G99" s="6">
-        <f t="shared" si="28"/>
-        <v>0.40944881889763779</v>
-      </c>
-      <c r="H99" s="6">
-        <f t="shared" si="29"/>
-        <v>0.43697478991596633</v>
-      </c>
-      <c r="I99" s="5"/>
-    </row>
-    <row r="100" spans="1:9">
-      <c r="A100" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="B100" s="7">
-        <v>80</v>
-      </c>
-      <c r="C100" s="7">
-        <v>72</v>
-      </c>
-      <c r="D100" s="7">
-        <v>47</v>
-      </c>
-      <c r="E100" s="7">
-        <f t="shared" si="23"/>
         <v>128</v>
       </c>
-      <c r="F100" s="8">
+      <c r="F110" s="8">
+        <f t="shared" si="31"/>
+        <v>0.52631578947368418</v>
+      </c>
+      <c r="G110" s="8">
+        <f t="shared" si="32"/>
+        <v>0.62992125984251968</v>
+      </c>
+      <c r="H110" s="8">
+        <f t="shared" si="33"/>
+        <v>0.57347670250896043</v>
+      </c>
+      <c r="I110" s="5"/>
+    </row>
+    <row r="111" spans="1:9">
+      <c r="A111" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="B111" s="10">
+        <f>AVERAGE(B103,B104,B105,B106,B107,B108,B109,B110)</f>
+        <v>67.75</v>
+      </c>
+      <c r="C111" s="10">
+        <f>AVERAGE(C103,C104,C105,C106,C107,C108,C109,C110)</f>
+        <v>70.625</v>
+      </c>
+      <c r="D111" s="10">
+        <f>AVERAGE(D103,D104,D105,D106,D107,D108,D109,D110)</f>
+        <v>59.25</v>
+      </c>
+      <c r="E111" s="10">
         <f t="shared" si="27"/>
-        <v>0.52631578947368418</v>
-      </c>
-      <c r="G100" s="8">
-        <f t="shared" si="28"/>
-        <v>0.62992125984251968</v>
-      </c>
-      <c r="H100" s="8">
-        <f t="shared" si="29"/>
-        <v>0.57347670250896043</v>
-      </c>
-      <c r="I100" s="5"/>
-    </row>
-    <row r="101" spans="1:9">
-      <c r="A101" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="B101" s="10">
-        <f>AVERAGE(B93,B94,B95,B96,B97,B98,B99,B100)</f>
-        <v>67.75</v>
-      </c>
-      <c r="C101" s="10">
-        <f>AVERAGE(C93,C94,C95,C96,C97,C98,C99,C100)</f>
-        <v>70.625</v>
-      </c>
-      <c r="D101" s="10">
-        <f>AVERAGE(D93,D94,D95,D96,D97,D98,D99,D100)</f>
-        <v>59.25</v>
-      </c>
-      <c r="E101" s="10">
-        <f t="shared" si="23"/>
         <v>129.375</v>
       </c>
-      <c r="F101" s="11">
-        <f>AVERAGE(F93,F94,F95,F96,F97,F98,F99,F100)</f>
+      <c r="F111" s="11">
+        <f>AVERAGE(F103,F104,F105,F106,F107,F108,F109,F110)</f>
         <v>0.48955989472660727</v>
       </c>
-      <c r="G101" s="11">
-        <f>AVERAGE(G93,G94,G95,G96,G97,G98,G99,G100)</f>
+      <c r="G111" s="11">
+        <f>AVERAGE(G103,G104,G105,G106,G107,G108,G109,G110)</f>
         <v>0.5334645669291338</v>
       </c>
-      <c r="H101" s="11">
-        <f>AVERAGE(H93,H94,H95,H96,H97,H98,H99,H100)</f>
+      <c r="H111" s="11">
+        <f>AVERAGE(H103,H104,H105,H106,H107,H108,H109,H110)</f>
         <v>0.50703120935034329</v>
       </c>
-      <c r="I101" s="9"/>
+      <c r="I111" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -6747,7 +7323,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr defaultRowHeight="14.35"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -6761,7 +7337,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="C1" s="18"/>
       <c r="D1" s="18"/>
@@ -6791,7 +7367,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="C3" s="18"/>
       <c r="D3" s="18"/>
@@ -6806,7 +7382,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="C4" s="18"/>
       <c r="D4" s="18"/>
@@ -6821,7 +7397,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="C5" s="18"/>
       <c r="D5" s="18"/>
@@ -6938,10 +7514,10 @@
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
@@ -6956,7 +7532,7 @@
         <v>19</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
@@ -6971,7 +7547,7 @@
         <v>21</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
@@ -6986,7 +7562,7 @@
         <v>23</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="C16" s="18"/>
       <c r="D16" s="18"/>
@@ -7027,7 +7603,7 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="3" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -7040,7 +7616,7 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="5" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="B20" s="5">
         <v>220</v>
@@ -7071,7 +7647,7 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="5" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="B21" s="5">
         <v>158</v>
@@ -7102,7 +7678,7 @@
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="7" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="B22" s="7">
         <v>200</v>
@@ -7133,7 +7709,7 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="3" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -7146,7 +7722,7 @@
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="7" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="B24" s="7">
         <v>266</v>
@@ -7177,7 +7753,7 @@
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="5" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="B25" s="5">
         <v>132</v>
@@ -7208,7 +7784,7 @@
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="5" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="B26" s="5">
         <v>204</v>
@@ -7239,7 +7815,7 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="3" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -7252,10 +7828,10 @@
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="5" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
@@ -7264,15 +7840,15 @@
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
       <c r="I28" s="5" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="5" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
@@ -7281,161 +7857,178 @@
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
       <c r="I29" s="5" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
+      <c r="A30" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="B32" s="5">
+        <v>205</v>
+      </c>
+      <c r="C32" s="5">
+        <v>331</v>
+      </c>
+      <c r="D32" s="5">
+        <v>115</v>
+      </c>
+      <c r="E32" s="5">
+        <f>1000-B32-C32-D32</f>
+        <v>349</v>
+      </c>
+      <c r="F32" s="6">
+        <f>IFERROR(B32/(B32+C32),0)</f>
+        <v>0.3824626865671642</v>
+      </c>
+      <c r="G32" s="6">
+        <f>IFERROR(B32/(B32+D32),0)</f>
+        <v>0.640625</v>
+      </c>
+      <c r="H32" s="6">
+        <f>IFERROR(2*F32*G32/(F32+G32),0)</f>
+        <v>0.47897196261682234</v>
+      </c>
+      <c r="I32" s="5"/>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="B33" s="7">
         <v>213</v>
       </c>
-      <c r="B31" s="5">
-        <v>205</v>
-      </c>
-      <c r="C31" s="5">
-        <v>331</v>
-      </c>
-      <c r="D31" s="5">
-        <v>115</v>
-      </c>
-      <c r="E31" s="5">
-        <f>1000-B31-C31-D31</f>
-        <v>349</v>
-      </c>
-      <c r="F31" s="6">
-        <f>IFERROR(B31/(B31+C31),0)</f>
-        <v>0.3824626865671642</v>
-      </c>
-      <c r="G31" s="6">
-        <f>IFERROR(B31/(B31+D31),0)</f>
-        <v>0.640625</v>
-      </c>
-      <c r="H31" s="6">
-        <f>IFERROR(2*F31*G31/(F31+G31),0)</f>
-        <v>0.47897196261682234</v>
-      </c>
-      <c r="I31" s="5"/>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B32" s="7">
-        <v>213</v>
-      </c>
-      <c r="C32" s="7">
+      <c r="C33" s="7">
         <v>351</v>
       </c>
-      <c r="D32" s="7">
+      <c r="D33" s="7">
         <v>107</v>
       </c>
-      <c r="E32" s="7">
-        <f>1000-B32-C32-D32</f>
+      <c r="E33" s="7">
+        <f>1000-B33-C33-D33</f>
         <v>329</v>
       </c>
-      <c r="F32" s="8">
-        <f>IFERROR(B32/(B32+C32),0)</f>
+      <c r="F33" s="8">
+        <f>IFERROR(B33/(B33+C33),0)</f>
         <v>0.37765957446808512</v>
       </c>
-      <c r="G32" s="8">
-        <f>IFERROR(B32/(B32+D32),0)</f>
+      <c r="G33" s="8">
+        <f>IFERROR(B33/(B33+D33),0)</f>
         <v>0.66562500000000002</v>
       </c>
-      <c r="H32" s="8">
-        <f>IFERROR(2*F32*G32/(F32+G32),0)</f>
+      <c r="H33" s="8">
+        <f>IFERROR(2*F33*G33/(F33+G33),0)</f>
         <v>0.48190045248868779</v>
       </c>
-      <c r="I32" s="5"/>
-    </row>
-    <row r="33" spans="1:9">
-      <c r="A33" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
+      <c r="I33" s="5"/>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B34" s="7">
-        <v>241</v>
-      </c>
-      <c r="C34" s="7">
-        <v>402</v>
-      </c>
-      <c r="D34" s="7">
-        <v>79</v>
-      </c>
-      <c r="E34" s="7">
-        <f>1000-B34-C34-D34</f>
-        <v>278</v>
-      </c>
-      <c r="F34" s="8">
-        <f>IFERROR(B34/(B34+C34),0)</f>
-        <v>0.37480559875583203</v>
-      </c>
-      <c r="G34" s="8">
-        <f>IFERROR(B34/(B34+D34),0)</f>
-        <v>0.75312500000000004</v>
-      </c>
-      <c r="H34" s="8">
-        <f>IFERROR(2*F34*G34/(F34+G34),0)</f>
-        <v>0.50051921079958461</v>
-      </c>
-      <c r="I34" s="5" t="s">
-        <v>217</v>
-      </c>
+      <c r="A34" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="7" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="B35" s="7">
-        <v>281</v>
+        <v>241</v>
       </c>
       <c r="C35" s="7">
-        <v>487</v>
+        <v>402</v>
       </c>
       <c r="D35" s="7">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="E35" s="7">
         <f>1000-B35-C35-D35</f>
-        <v>193</v>
+        <v>278</v>
       </c>
       <c r="F35" s="8">
         <f>IFERROR(B35/(B35+C35),0)</f>
-        <v>0.36588541666666669</v>
+        <v>0.37480559875583203</v>
       </c>
       <c r="G35" s="8">
         <f>IFERROR(B35/(B35+D35),0)</f>
-        <v>0.87812500000000004</v>
+        <v>0.75312500000000004</v>
       </c>
       <c r="H35" s="8">
         <f>IFERROR(2*F35*G35/(F35+G35),0)</f>
+        <v>0.50051921079958461</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="B36" s="7">
+        <v>281</v>
+      </c>
+      <c r="C36" s="7">
+        <v>487</v>
+      </c>
+      <c r="D36" s="7">
+        <v>39</v>
+      </c>
+      <c r="E36" s="7">
+        <f>1000-B36-C36-D36</f>
+        <v>193</v>
+      </c>
+      <c r="F36" s="8">
+        <f>IFERROR(B36/(B36+C36),0)</f>
+        <v>0.36588541666666669</v>
+      </c>
+      <c r="G36" s="8">
+        <f>IFERROR(B36/(B36+D36),0)</f>
+        <v>0.87812500000000004</v>
+      </c>
+      <c r="H36" s="8">
+        <f>IFERROR(2*F36*G36/(F36+G36),0)</f>
         <v>0.51654411764705888</v>
       </c>
-      <c r="I35" s="5" t="s">
-        <v>217</v>
+      <c r="I36" s="5" t="s">
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -7463,7 +8056,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr defaultRowHeight="14.35"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -7477,7 +8070,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="C1" s="18"/>
       <c r="D1" s="18"/>
@@ -7507,7 +8100,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="C3" s="18"/>
       <c r="D3" s="18"/>
@@ -7522,7 +8115,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="C4" s="18"/>
       <c r="D4" s="18"/>
@@ -7537,7 +8130,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="C5" s="18"/>
       <c r="D5" s="18"/>
@@ -7654,10 +8247,10 @@
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
@@ -7669,10 +8262,10 @@
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
@@ -7687,7 +8280,7 @@
         <v>21</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
@@ -7743,7 +8336,7 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="3" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -7849,7 +8442,7 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="3" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -7955,7 +8548,7 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="7" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="B27" s="7">
         <v>83</v>
@@ -7983,12 +8576,12 @@
         <v>0.58450704225352113</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="3" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -8029,7 +8622,7 @@
         <v>0.44979919678714864</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>231</v>
+        <v>250</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -8062,12 +8655,12 @@
         <v>0.56804733727810641</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="3" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -8080,7 +8673,7 @@
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="7" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="B32" s="7">
         <v>96</v>
@@ -8108,12 +8701,12 @@
         <v>0.55976676384839652</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="7" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="B33" s="7">
         <v>111</v>
@@ -8141,12 +8734,12 @@
         <v>0.5620253164556962</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="3" t="s">
-        <v>235</v>
+        <v>87</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -8159,65 +8752,111 @@
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="7" t="s">
-        <v>236</v>
+        <v>88</v>
       </c>
       <c r="B35" s="7">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C35" s="7">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D35" s="7">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E35" s="7">
         <f>327-B35-C35-D35</f>
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F35" s="8">
         <f>IFERROR(B35/(B35+C35),0)</f>
-        <v>0.41984732824427479</v>
+        <v>0.42379182156133827</v>
       </c>
       <c r="G35" s="8">
         <f>IFERROR(B35/(B35+D35),0)</f>
-        <v>0.86614173228346458</v>
+        <v>0.89763779527559051</v>
       </c>
       <c r="H35" s="8">
         <f>IFERROR(2*F35*G35/(F35+G35),0)</f>
+        <v>0.57575757575757569</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="B37" s="7">
+        <v>110</v>
+      </c>
+      <c r="C37" s="7">
+        <v>152</v>
+      </c>
+      <c r="D37" s="7">
+        <v>17</v>
+      </c>
+      <c r="E37" s="7">
+        <f>327-B37-C37-D37</f>
+        <v>48</v>
+      </c>
+      <c r="F37" s="8">
+        <f>IFERROR(B37/(B37+C37),0)</f>
+        <v>0.41984732824427479</v>
+      </c>
+      <c r="G37" s="8">
+        <f>IFERROR(B37/(B37+D37),0)</f>
+        <v>0.86614173228346458</v>
+      </c>
+      <c r="H37" s="8">
+        <f>IFERROR(2*F37*G37/(F37+G37),0)</f>
         <v>0.56555269922879181</v>
       </c>
-      <c r="I35" s="5"/>
-    </row>
-    <row r="36" spans="1:9">
-      <c r="A36" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="B36" s="7">
+      <c r="I37" s="5"/>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="B38" s="7">
         <v>87</v>
       </c>
-      <c r="C36" s="7">
+      <c r="C38" s="7">
         <v>97</v>
       </c>
-      <c r="D36" s="7">
+      <c r="D38" s="7">
         <v>40</v>
       </c>
-      <c r="E36" s="7">
-        <f>327-B36-C36-D36</f>
+      <c r="E38" s="7">
+        <f>327-B38-C38-D38</f>
         <v>103</v>
       </c>
-      <c r="F36" s="8">
-        <f>IFERROR(B36/(B36+C36),0)</f>
+      <c r="F38" s="8">
+        <f>IFERROR(B38/(B38+C38),0)</f>
         <v>0.47282608695652173</v>
       </c>
-      <c r="G36" s="8">
-        <f>IFERROR(B36/(B36+D36),0)</f>
+      <c r="G38" s="8">
+        <f>IFERROR(B38/(B38+D38),0)</f>
         <v>0.68503937007874016</v>
       </c>
-      <c r="H36" s="8">
-        <f>IFERROR(2*F36*G36/(F36+G36),0)</f>
+      <c r="H38" s="8">
+        <f>IFERROR(2*F38*G38/(F38+G38),0)</f>
         <v>0.55948553054662387</v>
       </c>
-      <c r="I36" s="5"/>
+      <c r="I38" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -8244,7 +8883,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr defaultRowHeight="14.35"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -8258,7 +8897,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="C1" s="18"/>
       <c r="D1" s="18"/>
@@ -8273,7 +8912,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="C2" s="18"/>
       <c r="D2" s="18"/>
@@ -8288,7 +8927,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="C3" s="18"/>
       <c r="D3" s="18"/>
@@ -8303,7 +8942,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C4" s="18"/>
       <c r="D4" s="18"/>
@@ -8318,7 +8957,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="C5" s="18"/>
       <c r="D5" s="18"/>
@@ -8435,10 +9074,10 @@
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
@@ -8450,10 +9089,10 @@
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
@@ -8468,7 +9107,7 @@
         <v>21</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
@@ -8480,10 +9119,10 @@
     </row>
     <row r="16" spans="1:9" ht="30" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="C16" s="18"/>
       <c r="D16" s="18"/>
@@ -8539,7 +9178,7 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="3" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -8552,7 +9191,7 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="5" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="B21" s="5">
         <v>2</v>
@@ -8583,7 +9222,7 @@
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="5" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="B22" s="5">
         <v>3</v>
@@ -8614,7 +9253,7 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="7" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="B23" s="7">
         <v>8</v>
@@ -8645,7 +9284,7 @@
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="3" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -8658,7 +9297,7 @@
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="5" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="B25" s="5">
         <v>9</v>
@@ -8689,7 +9328,7 @@
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="5" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="B26" s="5">
         <v>3</v>
@@ -8720,7 +9359,7 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="7" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="B27" s="7">
         <v>12</v>
@@ -8751,10 +9390,10 @@
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="5" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
@@ -8763,12 +9402,12 @@
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
       <c r="I28" s="5" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="3" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -8812,7 +9451,7 @@
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="5" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="B31" s="5">
         <v>9</v>
@@ -8843,7 +9482,7 @@
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="3" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -8856,7 +9495,7 @@
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="7" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="B33" s="7">
         <v>9</v>
@@ -8884,12 +9523,12 @@
         <v>0.15789473684210525</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="7" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="B34" s="7">
         <v>13</v>
@@ -8917,12 +9556,12 @@
         <v>0.15204678362573096</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="3" t="s">
-        <v>262</v>
+        <v>87</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -8935,65 +9574,111 @@
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="7" t="s">
-        <v>263</v>
+        <v>282</v>
       </c>
       <c r="B36" s="7">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C36" s="7">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="D36" s="7">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E36" s="7">
         <f>327-B36-C36-D36</f>
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="F36" s="8">
         <f>IFERROR(B36/(B36+C36),0)</f>
-        <v>5.9602649006622516E-2</v>
+        <v>7.4712643678160925E-2</v>
       </c>
       <c r="G36" s="8">
         <f>IFERROR(B36/(B36+D36),0)</f>
-        <v>0.6</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="H36" s="8">
         <f>IFERROR(2*F36*G36/(F36+G36),0)</f>
+        <v>0.13756613756613759</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="B38" s="7">
+        <v>9</v>
+      </c>
+      <c r="C38" s="7">
+        <v>142</v>
+      </c>
+      <c r="D38" s="7">
+        <v>6</v>
+      </c>
+      <c r="E38" s="7">
+        <f>327-B38-C38-D38</f>
+        <v>170</v>
+      </c>
+      <c r="F38" s="8">
+        <f>IFERROR(B38/(B38+C38),0)</f>
+        <v>5.9602649006622516E-2</v>
+      </c>
+      <c r="G38" s="8">
+        <f>IFERROR(B38/(B38+D38),0)</f>
+        <v>0.6</v>
+      </c>
+      <c r="H38" s="8">
+        <f>IFERROR(2*F38*G38/(F38+G38),0)</f>
         <v>0.10843373493975905</v>
       </c>
-      <c r="I36" s="5"/>
-    </row>
-    <row r="37" spans="1:9">
-      <c r="A37" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="B37" s="7">
+      <c r="I38" s="5"/>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="B39" s="7">
         <v>3</v>
       </c>
-      <c r="C37" s="7">
+      <c r="C39" s="7">
         <v>52</v>
       </c>
-      <c r="D37" s="7">
+      <c r="D39" s="7">
         <v>12</v>
       </c>
-      <c r="E37" s="7">
-        <f>327-B37-C37-D37</f>
+      <c r="E39" s="7">
+        <f>327-B39-C39-D39</f>
         <v>260</v>
       </c>
-      <c r="F37" s="8">
-        <f>IFERROR(B37/(B37+C37),0)</f>
+      <c r="F39" s="8">
+        <f>IFERROR(B39/(B39+C39),0)</f>
         <v>5.4545454545454543E-2</v>
       </c>
-      <c r="G37" s="8">
-        <f>IFERROR(B37/(B37+D37),0)</f>
+      <c r="G39" s="8">
+        <f>IFERROR(B39/(B39+D39),0)</f>
         <v>0.2</v>
       </c>
-      <c r="H37" s="8">
-        <f>IFERROR(2*F37*G37/(F37+G37),0)</f>
+      <c r="H39" s="8">
+        <f>IFERROR(2*F39*G39/(F39+G39),0)</f>
         <v>8.5714285714285715E-2</v>
       </c>
-      <c r="I37" s="5"/>
+      <c r="I39" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -9021,7 +9706,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr defaultRowHeight="14.35"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -9035,7 +9720,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>265</v>
+        <v>286</v>
       </c>
       <c r="C1" s="18"/>
       <c r="D1" s="18"/>
@@ -9050,7 +9735,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="C2" s="18"/>
       <c r="D2" s="18"/>
@@ -9065,7 +9750,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="C3" s="18"/>
       <c r="D3" s="18"/>
@@ -9080,7 +9765,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C4" s="18"/>
       <c r="D4" s="18"/>
@@ -9095,7 +9780,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="C5" s="18"/>
       <c r="D5" s="18"/>
@@ -9212,10 +9897,10 @@
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
@@ -9227,10 +9912,10 @@
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
@@ -9245,7 +9930,7 @@
         <v>21</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
@@ -9257,10 +9942,10 @@
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="C16" s="18"/>
       <c r="D16" s="18"/>
@@ -9316,7 +10001,7 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="3" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -9329,7 +10014,7 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="7" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="B21" s="7">
         <v>14</v>
@@ -9360,7 +10045,7 @@
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="5" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="B22" s="5">
         <v>42</v>
@@ -9391,7 +10076,7 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="5" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="B23" s="5">
         <v>15</v>
@@ -9422,7 +10107,7 @@
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="3" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -9435,7 +10120,7 @@
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="5" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="B25" s="5">
         <v>24</v>
@@ -9466,7 +10151,7 @@
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="5" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="B26" s="5">
         <v>20</v>
@@ -9497,7 +10182,7 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="7" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="B27" s="7">
         <v>27</v>
@@ -9528,10 +10213,10 @@
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="5" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
@@ -9540,12 +10225,12 @@
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
       <c r="I28" s="5" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="3" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -9589,7 +10274,7 @@
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="5" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="B31" s="5">
         <v>21</v>
@@ -9620,7 +10305,7 @@
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="3" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -9633,7 +10318,7 @@
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="7" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="B33" s="7">
         <v>30</v>
@@ -9661,12 +10346,12 @@
         <v>0.33707865168539325</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="7" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="B34" s="7">
         <v>46</v>
@@ -9694,12 +10379,12 @@
         <v>0.31292517006802723</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="3" t="s">
-        <v>262</v>
+        <v>87</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -9712,65 +10397,111 @@
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="7" t="s">
-        <v>263</v>
+        <v>282</v>
       </c>
       <c r="B36" s="7">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C36" s="7">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="D36" s="7">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E36" s="7">
         <f>327-B36-C36-D36</f>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="F36" s="8">
         <f>IFERROR(B36/(B36+C36),0)</f>
-        <v>0.18260869565217391</v>
+        <v>0.18775510204081633</v>
       </c>
       <c r="G36" s="8">
         <f>IFERROR(B36/(B36+D36),0)</f>
-        <v>0.8571428571428571</v>
+        <v>0.93877551020408168</v>
       </c>
       <c r="H36" s="8">
         <f>IFERROR(2*F36*G36/(F36+G36),0)</f>
+        <v>0.31292517006802723</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="B38" s="7">
+        <v>42</v>
+      </c>
+      <c r="C38" s="7">
+        <v>188</v>
+      </c>
+      <c r="D38" s="7">
+        <v>7</v>
+      </c>
+      <c r="E38" s="7">
+        <f>327-B38-C38-D38</f>
+        <v>90</v>
+      </c>
+      <c r="F38" s="8">
+        <f>IFERROR(B38/(B38+C38),0)</f>
+        <v>0.18260869565217391</v>
+      </c>
+      <c r="G38" s="8">
+        <f>IFERROR(B38/(B38+D38),0)</f>
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="H38" s="8">
+        <f>IFERROR(2*F38*G38/(F38+G38),0)</f>
         <v>0.30107526881720431</v>
       </c>
-      <c r="I36" s="5"/>
-    </row>
-    <row r="37" spans="1:9">
-      <c r="A37" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="B37" s="7">
+      <c r="I38" s="5"/>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="B39" s="7">
         <v>24</v>
       </c>
-      <c r="C37" s="7">
+      <c r="C39" s="7">
         <v>62</v>
       </c>
-      <c r="D37" s="7">
+      <c r="D39" s="7">
         <v>25</v>
       </c>
-      <c r="E37" s="7">
-        <f>327-B37-C37-D37</f>
+      <c r="E39" s="7">
+        <f>327-B39-C39-D39</f>
         <v>216</v>
       </c>
-      <c r="F37" s="8">
-        <f>IFERROR(B37/(B37+C37),0)</f>
+      <c r="F39" s="8">
+        <f>IFERROR(B39/(B39+C39),0)</f>
         <v>0.27906976744186046</v>
       </c>
-      <c r="G37" s="8">
-        <f>IFERROR(B37/(B37+D37),0)</f>
+      <c r="G39" s="8">
+        <f>IFERROR(B39/(B39+D39),0)</f>
         <v>0.48979591836734693</v>
       </c>
-      <c r="H37" s="8">
-        <f>IFERROR(2*F37*G37/(F37+G37),0)</f>
+      <c r="H39" s="8">
+        <f>IFERROR(2*F39*G39/(F39+G39),0)</f>
         <v>0.35555555555555562</v>
       </c>
-      <c r="I37" s="5"/>
+      <c r="I39" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -9798,7 +10529,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr defaultRowHeight="14.35"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -9812,7 +10543,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="C1" s="18"/>
       <c r="D1" s="18"/>
@@ -9827,7 +10558,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="C2" s="18"/>
       <c r="D2" s="18"/>
@@ -9842,7 +10573,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="C3" s="18"/>
       <c r="D3" s="18"/>
@@ -9857,7 +10588,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C4" s="18"/>
       <c r="D4" s="18"/>
@@ -9872,7 +10603,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="C5" s="18"/>
       <c r="D5" s="18"/>
@@ -9989,10 +10720,10 @@
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
@@ -10004,10 +10735,10 @@
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
@@ -10022,7 +10753,7 @@
         <v>21</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
@@ -10034,10 +10765,10 @@
     </row>
     <row r="16" spans="1:9" ht="30" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="C16" s="18"/>
       <c r="D16" s="18"/>
@@ -10093,7 +10824,7 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="3" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -10106,7 +10837,7 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="7" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="B21" s="7">
         <v>8</v>
@@ -10137,7 +10868,7 @@
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="5" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="B22" s="5">
         <v>9</v>
@@ -10168,7 +10899,7 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="5" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="B23" s="5">
         <v>4</v>
@@ -10199,7 +10930,7 @@
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="3" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -10212,7 +10943,7 @@
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="5" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="B25" s="5">
         <v>8</v>
@@ -10243,7 +10974,7 @@
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="5" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="B26" s="5">
         <v>9</v>
@@ -10274,7 +11005,7 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="7" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="B27" s="7">
         <v>7</v>
@@ -10305,10 +11036,10 @@
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="5" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
@@ -10317,12 +11048,12 @@
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
       <c r="I28" s="5" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="3" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -10366,7 +11097,7 @@
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="5" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="B31" s="5">
         <v>9</v>
@@ -10397,7 +11128,7 @@
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="3" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -10410,7 +11141,7 @@
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="7" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="B33" s="7">
         <v>9</v>
@@ -10438,12 +11169,12 @@
         <v>0.21428571428571425</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="7" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="B34" s="7">
         <v>10</v>
@@ -10471,12 +11202,12 @@
         <v>0.16393442622950818</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="3" t="s">
-        <v>262</v>
+        <v>87</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -10489,65 +11220,111 @@
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="7" t="s">
-        <v>263</v>
+        <v>282</v>
       </c>
       <c r="B36" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C36" s="7">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D36" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E36" s="7">
         <f>327-B36-C36-D36</f>
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="F36" s="8">
         <f>IFERROR(B36/(B36+C36),0)</f>
-        <v>8.6538461538461536E-2</v>
+        <v>9.0090090090090086E-2</v>
       </c>
       <c r="G36" s="8">
         <f>IFERROR(B36/(B36+D36),0)</f>
-        <v>0.69230769230769229</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="H36" s="8">
         <f>IFERROR(2*F36*G36/(F36+G36),0)</f>
+        <v>0.16129032258064516</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="B38" s="7">
+        <v>9</v>
+      </c>
+      <c r="C38" s="7">
+        <v>95</v>
+      </c>
+      <c r="D38" s="7">
+        <v>4</v>
+      </c>
+      <c r="E38" s="7">
+        <f>327-B38-C38-D38</f>
+        <v>219</v>
+      </c>
+      <c r="F38" s="8">
+        <f>IFERROR(B38/(B38+C38),0)</f>
+        <v>8.6538461538461536E-2</v>
+      </c>
+      <c r="G38" s="8">
+        <f>IFERROR(B38/(B38+D38),0)</f>
+        <v>0.69230769230769229</v>
+      </c>
+      <c r="H38" s="8">
+        <f>IFERROR(2*F38*G38/(F38+G38),0)</f>
         <v>0.15384615384615383</v>
       </c>
-      <c r="I36" s="5"/>
-    </row>
-    <row r="37" spans="1:9">
-      <c r="A37" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="B37" s="7">
+      <c r="I38" s="5"/>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="B39" s="7">
         <v>8</v>
       </c>
-      <c r="C37" s="7">
+      <c r="C39" s="7">
         <v>33</v>
       </c>
-      <c r="D37" s="7">
+      <c r="D39" s="7">
         <v>5</v>
       </c>
-      <c r="E37" s="7">
-        <f>327-B37-C37-D37</f>
+      <c r="E39" s="7">
+        <f>327-B39-C39-D39</f>
         <v>281</v>
       </c>
-      <c r="F37" s="8">
-        <f>IFERROR(B37/(B37+C37),0)</f>
+      <c r="F39" s="8">
+        <f>IFERROR(B39/(B39+C39),0)</f>
         <v>0.1951219512195122</v>
       </c>
-      <c r="G37" s="8">
-        <f>IFERROR(B37/(B37+D37),0)</f>
+      <c r="G39" s="8">
+        <f>IFERROR(B39/(B39+D39),0)</f>
         <v>0.61538461538461542</v>
       </c>
-      <c r="H37" s="8">
-        <f>IFERROR(2*F37*G37/(F37+G37),0)</f>
+      <c r="H39" s="8">
+        <f>IFERROR(2*F39*G39/(F39+G39),0)</f>
         <v>0.29629629629629634</v>
       </c>
-      <c r="I37" s="5"/>
+      <c r="I39" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -10575,7 +11352,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr defaultRowHeight="14.35"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -10589,7 +11366,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="C1" s="18"/>
       <c r="D1" s="18"/>
@@ -10604,7 +11381,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>280</v>
+        <v>301</v>
       </c>
       <c r="C2" s="18"/>
       <c r="D2" s="18"/>
@@ -10619,7 +11396,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="C3" s="18"/>
       <c r="D3" s="18"/>
@@ -10634,7 +11411,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C4" s="18"/>
       <c r="D4" s="18"/>
@@ -10649,7 +11426,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="C5" s="18"/>
       <c r="D5" s="18"/>
@@ -10766,10 +11543,10 @@
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
@@ -10781,10 +11558,10 @@
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>282</v>
+        <v>303</v>
       </c>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
@@ -10799,7 +11576,7 @@
         <v>21</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
@@ -10811,10 +11588,10 @@
     </row>
     <row r="16" spans="1:9" ht="30" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="C16" s="18"/>
       <c r="D16" s="18"/>
@@ -10870,7 +11647,7 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="3" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -10883,7 +11660,7 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="7" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="B21" s="7">
         <v>13</v>
@@ -10914,7 +11691,7 @@
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="5" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="B22" s="5">
         <v>15</v>
@@ -10945,7 +11722,7 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="5" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="B23" s="5">
         <v>13</v>
@@ -10976,7 +11753,7 @@
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="3" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -10989,7 +11766,7 @@
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="5" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="B25" s="5">
         <v>13</v>
@@ -11020,7 +11797,7 @@
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="7" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="B26" s="7">
         <v>20</v>
@@ -11051,7 +11828,7 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="5" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="B27" s="5">
         <v>11</v>
@@ -11082,10 +11859,10 @@
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="5" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
@@ -11094,12 +11871,12 @@
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
       <c r="I28" s="5" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="3" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -11143,7 +11920,7 @@
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="5" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="B31" s="5">
         <v>13</v>
@@ -11174,7 +11951,7 @@
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="3" t="s">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -11187,7 +11964,7 @@
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="7" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="B33" s="7">
         <v>17</v>
@@ -11215,12 +11992,12 @@
         <v>0.3863636363636363</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>285</v>
+        <v>306</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="7" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="B34" s="7">
         <v>21</v>
@@ -11248,12 +12025,12 @@
         <v>0.30215827338129492</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>285</v>
+        <v>306</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="3" t="s">
-        <v>262</v>
+        <v>87</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -11266,24 +12043,24 @@
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="7" t="s">
-        <v>263</v>
+        <v>282</v>
       </c>
       <c r="B36" s="7">
         <v>18</v>
       </c>
       <c r="C36" s="7">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D36" s="7">
         <v>7</v>
       </c>
       <c r="E36" s="7">
         <f>327-B36-C36-D36</f>
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="F36" s="8">
         <f>IFERROR(B36/(B36+C36),0)</f>
-        <v>0.17475728155339806</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="G36" s="8">
         <f>IFERROR(B36/(B36+D36),0)</f>
@@ -11291,40 +12068,86 @@
       </c>
       <c r="H36" s="8">
         <f>IFERROR(2*F36*G36/(F36+G36),0)</f>
+        <v>0.27067669172932329</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="B38" s="7">
+        <v>18</v>
+      </c>
+      <c r="C38" s="7">
+        <v>85</v>
+      </c>
+      <c r="D38" s="7">
+        <v>7</v>
+      </c>
+      <c r="E38" s="7">
+        <f>327-B38-C38-D38</f>
+        <v>217</v>
+      </c>
+      <c r="F38" s="8">
+        <f>IFERROR(B38/(B38+C38),0)</f>
+        <v>0.17475728155339806</v>
+      </c>
+      <c r="G38" s="8">
+        <f>IFERROR(B38/(B38+D38),0)</f>
+        <v>0.72</v>
+      </c>
+      <c r="H38" s="8">
+        <f>IFERROR(2*F38*G38/(F38+G38),0)</f>
         <v>0.28125</v>
       </c>
-      <c r="I36" s="5"/>
-    </row>
-    <row r="37" spans="1:9">
-      <c r="A37" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="B37" s="7">
+      <c r="I38" s="5"/>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="B39" s="7">
         <v>10</v>
       </c>
-      <c r="C37" s="7">
+      <c r="C39" s="7">
         <v>28</v>
       </c>
-      <c r="D37" s="7">
+      <c r="D39" s="7">
         <v>15</v>
       </c>
-      <c r="E37" s="7">
-        <f>327-B37-C37-D37</f>
+      <c r="E39" s="7">
+        <f>327-B39-C39-D39</f>
         <v>274</v>
       </c>
-      <c r="F37" s="8">
-        <f>IFERROR(B37/(B37+C37),0)</f>
+      <c r="F39" s="8">
+        <f>IFERROR(B39/(B39+C39),0)</f>
         <v>0.26315789473684209</v>
       </c>
-      <c r="G37" s="8">
-        <f>IFERROR(B37/(B37+D37),0)</f>
+      <c r="G39" s="8">
+        <f>IFERROR(B39/(B39+D39),0)</f>
         <v>0.4</v>
       </c>
-      <c r="H37" s="8">
-        <f>IFERROR(2*F37*G37/(F37+G37),0)</f>
+      <c r="H39" s="8">
+        <f>IFERROR(2*F39*G39/(F39+G39),0)</f>
         <v>0.31746031746031739</v>
       </c>
-      <c r="I37" s="5"/>
+      <c r="I39" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -11366,7 +12189,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="C1" s="18"/>
       <c r="D1" s="18"/>
@@ -11381,7 +12204,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="C2" s="18"/>
       <c r="D2" s="18"/>
@@ -11396,7 +12219,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="C3" s="18"/>
       <c r="D3" s="18"/>
@@ -11411,7 +12234,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="C4" s="18"/>
       <c r="D4" s="18"/>
@@ -11426,7 +12249,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="C5" s="18"/>
       <c r="D5" s="18"/>
@@ -11456,7 +12279,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
@@ -11468,7 +12291,7 @@
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="B8" s="17">
         <v>179</v>
@@ -11483,10 +12306,10 @@
     </row>
     <row r="9" spans="1:9" ht="30" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C9" s="18"/>
       <c r="D9" s="18"/>
@@ -11498,10 +12321,10 @@
     </row>
     <row r="10" spans="1:9" ht="45" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="C10" s="18"/>
       <c r="D10" s="18"/>
@@ -11513,10 +12336,10 @@
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="C11" s="18"/>
       <c r="D11" s="18"/>
@@ -11557,7 +12380,7 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="3" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -11570,7 +12393,7 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="5" t="s">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="B15" s="5">
         <v>17</v>
@@ -11601,7 +12424,7 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="5" t="s">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="B16" s="5">
         <v>6</v>
@@ -11632,7 +12455,7 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="7" t="s">
-        <v>302</v>
+        <v>323</v>
       </c>
       <c r="B17" s="7">
         <v>34</v>
@@ -11663,7 +12486,7 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="3" t="s">
-        <v>303</v>
+        <v>324</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -11676,7 +12499,7 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="5" t="s">
-        <v>304</v>
+        <v>325</v>
       </c>
       <c r="B19" s="5">
         <v>25</v>
@@ -11707,7 +12530,7 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="5" t="s">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="B20" s="5">
         <v>28</v>
@@ -11738,7 +12561,7 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="7" t="s">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="B21" s="7">
         <v>45</v>
